--- a/target.xlsx
+++ b/target.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kt\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\백업폴더\딱따구리\AI\강북도매 영업관리 포털\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6D2F4C9-EAB2-4EAB-B78D-78B6710D495E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF041A1-FAF9-4706-8057-7CAB65757FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F51F585E-D8DA-4EE1-A615-D4BBA305B88C}"/>
   </bookViews>
@@ -1296,25 +1296,25 @@
         <v>19</v>
       </c>
       <c r="K2" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L2" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M2" s="3">
         <v>0</v>
       </c>
       <c r="N2" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O2" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P2" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R2" s="3">
         <v>20</v>
@@ -1430,7 +1430,7 @@
         <v>16</v>
       </c>
       <c r="X3" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y3" s="3">
         <v>17</v>
@@ -1495,19 +1495,19 @@
         <v>0</v>
       </c>
       <c r="N4" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O4" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P4" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q4" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R4" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S4" s="3">
         <v>29</v>
@@ -1537,7 +1537,7 @@
         <v>0</v>
       </c>
       <c r="AB4" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AC4" s="3">
         <v>23</v>
@@ -1581,19 +1581,19 @@
         <v>22</v>
       </c>
       <c r="K5" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L5" s="3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M5" s="3">
         <v>0</v>
       </c>
       <c r="N5" s="3">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O5" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P5" s="3">
         <v>23</v>
@@ -1632,7 +1632,7 @@
         <v>0</v>
       </c>
       <c r="AB5" s="3">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AC5" s="3">
         <v>24</v>
@@ -1649,13 +1649,13 @@
         <v>9</v>
       </c>
       <c r="B6" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6" s="3">
         <v>35</v>
@@ -1667,25 +1667,25 @@
         <v>40</v>
       </c>
       <c r="H6" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I6" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J6" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K6" s="3">
         <v>27</v>
       </c>
       <c r="L6" s="3">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M6" s="3">
         <v>0</v>
       </c>
       <c r="N6" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O6" s="3">
         <v>27</v>
@@ -1700,25 +1700,25 @@
         <v>27</v>
       </c>
       <c r="S6" s="3">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="T6" s="3">
         <v>0</v>
       </c>
       <c r="U6" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V6" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="W6" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="X6" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Y6" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z6" s="3">
         <v>36</v>
@@ -1860,16 +1860,16 @@
         <v>16</v>
       </c>
       <c r="I8" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J8" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K8" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L8" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -1955,16 +1955,16 @@
         <v>18</v>
       </c>
       <c r="I9" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J9" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K9" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L9" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M9" s="3">
         <v>0</v>
@@ -2059,16 +2059,16 @@
         <v>17</v>
       </c>
       <c r="L10" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M10" s="3">
         <v>0</v>
       </c>
       <c r="N10" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O10" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P10" s="3">
         <v>18</v>
@@ -2107,7 +2107,7 @@
         <v>0</v>
       </c>
       <c r="AB10" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AC10" s="3">
         <v>19</v>
@@ -2325,7 +2325,7 @@
         <v>0</v>
       </c>
       <c r="AB2" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC2" s="7">
         <v>5</v>
@@ -2342,13 +2342,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" s="7">
         <v>5</v>
@@ -2360,16 +2360,16 @@
         <v>5</v>
       </c>
       <c r="H3" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K3" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L3" s="7">
         <v>5</v>
@@ -2381,16 +2381,16 @@
         <v>5</v>
       </c>
       <c r="O3" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P3" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q3" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R3" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S3" s="7">
         <v>5</v>
@@ -2414,22 +2414,22 @@
         <v>3</v>
       </c>
       <c r="Z3" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA3" s="7">
         <v>0</v>
       </c>
       <c r="AB3" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AC3" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD3" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE3" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.45">
@@ -2616,7 +2616,7 @@
         <v>4</v>
       </c>
       <c r="AD5" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE5" s="7">
         <v>3</v>
@@ -2708,7 +2708,7 @@
         <v>7</v>
       </c>
       <c r="AC6" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD6" s="7">
         <v>4</v>
@@ -2785,7 +2785,7 @@
         <v>4</v>
       </c>
       <c r="W7" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X7" s="7">
         <v>3</v>
@@ -2895,7 +2895,7 @@
         <v>0</v>
       </c>
       <c r="AB8" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC8" s="7">
         <v>5</v>
@@ -2981,7 +2981,7 @@
         <v>3</v>
       </c>
       <c r="Y9" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z9" s="7">
         <v>2</v>
@@ -3079,7 +3079,7 @@
         <v>3</v>
       </c>
       <c r="Z10" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA10" s="7">
         <v>0</v>

--- a/target.xlsx
+++ b/target.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\백업폴더\딱따구리\AI\강북도매 영업관리 포털\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216155BB-8B8A-4212-86D3-6FE355FB41B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF056B8-4593-45FE-98D7-8ECC7927CB55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F51F585E-D8DA-4EE1-A615-D4BBA305B88C}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F51F585E-D8DA-4EE1-A615-D4BBA305B88C}"/>
   </bookViews>
   <sheets>
     <sheet name="무선목표" sheetId="2" r:id="rId1"/>
@@ -1275,10 +1275,10 @@
         <v>19</v>
       </c>
       <c r="I2" s="4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J2" s="4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K2" s="4">
         <v>0</v>
@@ -1474,22 +1474,22 @@
         <v>21</v>
       </c>
       <c r="J4" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K4" s="4">
         <v>0</v>
       </c>
       <c r="L4" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M4" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N4" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O4" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P4" s="4">
         <v>22</v>
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="4">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F5" s="4">
         <v>22</v>
@@ -1578,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="L5" s="4">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M5" s="4">
         <v>22</v>
@@ -1587,7 +1587,7 @@
         <v>22</v>
       </c>
       <c r="O5" s="4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P5" s="4">
         <v>23</v>
@@ -1599,7 +1599,7 @@
         <v>0</v>
       </c>
       <c r="S5" s="4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T5" s="4">
         <v>23</v>
@@ -1620,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="Z5" s="4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA5" s="4">
         <v>23</v>
@@ -1632,7 +1632,7 @@
         <v>23</v>
       </c>
       <c r="AD5" s="4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE5" s="4">
         <v>29</v>
@@ -1706,22 +1706,22 @@
         <v>27</v>
       </c>
       <c r="V6" s="4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="W6" s="4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="X6" s="4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y6" s="4">
         <v>0</v>
       </c>
       <c r="Z6" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AA6" s="4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AB6" s="4">
         <v>28</v>
@@ -1872,13 +1872,13 @@
         <v>0</v>
       </c>
       <c r="L8" s="4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M8" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N8" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O8" s="4">
         <v>17</v>
@@ -1982,7 +1982,7 @@
         <v>18</v>
       </c>
       <c r="P9" s="4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q9" s="4">
         <v>25</v>
@@ -2068,10 +2068,10 @@
         <v>0</v>
       </c>
       <c r="L10" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M10" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N10" s="4">
         <v>18</v>
@@ -2256,14 +2256,14 @@
         <v>5</v>
       </c>
       <c r="C2" s="4">
+        <v>6</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
         <v>7</v>
       </c>
-      <c r="D2" s="4">
-        <v>0</v>
-      </c>
-      <c r="E2" s="4">
-        <v>8</v>
-      </c>
       <c r="F2" s="4">
         <v>5</v>
       </c>
@@ -2277,14 +2277,14 @@
         <v>5</v>
       </c>
       <c r="J2" s="4">
+        <v>6</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0</v>
+      </c>
+      <c r="L2" s="4">
         <v>7</v>
       </c>
-      <c r="K2" s="4">
-        <v>0</v>
-      </c>
-      <c r="L2" s="4">
-        <v>8</v>
-      </c>
       <c r="M2" s="4">
         <v>5</v>
       </c>
@@ -2298,14 +2298,14 @@
         <v>5</v>
       </c>
       <c r="Q2" s="4">
+        <v>6</v>
+      </c>
+      <c r="R2" s="4">
+        <v>0</v>
+      </c>
+      <c r="S2" s="4">
         <v>7</v>
       </c>
-      <c r="R2" s="4">
-        <v>0</v>
-      </c>
-      <c r="S2" s="4">
-        <v>8</v>
-      </c>
       <c r="T2" s="4">
         <v>5</v>
       </c>
@@ -2319,14 +2319,14 @@
         <v>5</v>
       </c>
       <c r="X2" s="4">
+        <v>6</v>
+      </c>
+      <c r="Y2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="4">
         <v>7</v>
       </c>
-      <c r="Y2" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="4">
-        <v>8</v>
-      </c>
       <c r="AA2" s="4">
         <v>5</v>
       </c>
@@ -2334,13 +2334,13 @@
         <v>5</v>
       </c>
       <c r="AC2" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AD2" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE2" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF2" s="4">
         <v>0</v>
@@ -2530,7 +2530,7 @@
         <v>4</v>
       </c>
       <c r="AC4" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD4" s="4">
         <v>5</v>
@@ -2619,7 +2619,7 @@
         <v>0</v>
       </c>
       <c r="Z5" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA5" s="4">
         <v>4</v>
@@ -2631,7 +2631,7 @@
         <v>4</v>
       </c>
       <c r="AD5" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE5" s="4">
         <v>5</v>
@@ -2720,7 +2720,7 @@
         <v>9</v>
       </c>
       <c r="AA6" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB6" s="4">
         <v>5</v>
@@ -2815,7 +2815,7 @@
         <v>0</v>
       </c>
       <c r="Z7" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA7" s="4">
         <v>5</v>
@@ -2922,7 +2922,7 @@
         <v>4</v>
       </c>
       <c r="AC8" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD8" s="4">
         <v>5</v>
@@ -3020,10 +3020,10 @@
         <v>3</v>
       </c>
       <c r="AC9" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD9" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE9" s="4">
         <v>5</v>

--- a/target.xlsx
+++ b/target.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\백업폴더\딱따구리\AI\강북도매 영업관리 포털\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF056B8-4593-45FE-98D7-8ECC7927CB55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F575D52-7364-4D52-9137-4A2F9B3F4967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F51F585E-D8DA-4EE1-A615-D4BBA305B88C}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F51F585E-D8DA-4EE1-A615-D4BBA305B88C}"/>
   </bookViews>
   <sheets>
     <sheet name="무선목표" sheetId="2" r:id="rId1"/>
@@ -683,7 +683,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -701,6 +701,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="150">
@@ -1143,992 +1146,962 @@
   <sheetPr>
     <tabColor theme="1"/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AE10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="32" width="5.25" style="1" customWidth="1"/>
-    <col min="33" max="16384" width="9" style="1"/>
+    <col min="2" max="31" width="5.25" style="1" customWidth="1"/>
+    <col min="32" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="2">
-        <v>46143</v>
-      </c>
-      <c r="C1" s="2">
-        <v>46144</v>
-      </c>
-      <c r="D1" s="2">
-        <v>46145</v>
-      </c>
-      <c r="E1" s="2">
-        <v>46146</v>
-      </c>
-      <c r="F1" s="2">
-        <v>46147</v>
-      </c>
-      <c r="G1" s="2">
-        <v>46148</v>
-      </c>
-      <c r="H1" s="2">
-        <v>46149</v>
-      </c>
-      <c r="I1" s="2">
-        <v>46150</v>
-      </c>
-      <c r="J1" s="2">
-        <v>46151</v>
-      </c>
-      <c r="K1" s="2">
-        <v>46152</v>
-      </c>
-      <c r="L1" s="2">
-        <v>46153</v>
-      </c>
-      <c r="M1" s="2">
-        <v>46154</v>
-      </c>
-      <c r="N1" s="2">
-        <v>46155</v>
-      </c>
-      <c r="O1" s="2">
-        <v>46156</v>
-      </c>
-      <c r="P1" s="2">
-        <v>46157</v>
-      </c>
-      <c r="Q1" s="2">
-        <v>46158</v>
-      </c>
-      <c r="R1" s="2">
-        <v>46159</v>
-      </c>
-      <c r="S1" s="2">
-        <v>46160</v>
-      </c>
-      <c r="T1" s="2">
-        <v>46161</v>
-      </c>
-      <c r="U1" s="2">
-        <v>46162</v>
-      </c>
-      <c r="V1" s="2">
-        <v>46163</v>
-      </c>
-      <c r="W1" s="2">
-        <v>46164</v>
-      </c>
-      <c r="X1" s="2">
-        <v>46165</v>
-      </c>
-      <c r="Y1" s="2">
-        <v>46166</v>
-      </c>
-      <c r="Z1" s="2">
-        <v>46167</v>
-      </c>
-      <c r="AA1" s="2">
-        <v>46168</v>
-      </c>
-      <c r="AB1" s="2">
-        <v>46169</v>
-      </c>
-      <c r="AC1" s="2">
-        <v>46170</v>
-      </c>
-      <c r="AD1" s="2">
-        <v>46171</v>
-      </c>
-      <c r="AE1" s="2">
-        <v>46172</v>
-      </c>
-      <c r="AF1" s="2">
-        <v>46173</v>
+      <c r="B1" s="6">
+        <v>46174</v>
+      </c>
+      <c r="C1" s="6">
+        <v>46175</v>
+      </c>
+      <c r="D1" s="6">
+        <v>46176</v>
+      </c>
+      <c r="E1" s="6">
+        <v>46177</v>
+      </c>
+      <c r="F1" s="6">
+        <v>46178</v>
+      </c>
+      <c r="G1" s="6">
+        <v>46179</v>
+      </c>
+      <c r="H1" s="6">
+        <v>46180</v>
+      </c>
+      <c r="I1" s="6">
+        <v>46181</v>
+      </c>
+      <c r="J1" s="6">
+        <v>46182</v>
+      </c>
+      <c r="K1" s="6">
+        <v>46183</v>
+      </c>
+      <c r="L1" s="6">
+        <v>46184</v>
+      </c>
+      <c r="M1" s="6">
+        <v>46185</v>
+      </c>
+      <c r="N1" s="6">
+        <v>46186</v>
+      </c>
+      <c r="O1" s="6">
+        <v>46187</v>
+      </c>
+      <c r="P1" s="6">
+        <v>46188</v>
+      </c>
+      <c r="Q1" s="6">
+        <v>46189</v>
+      </c>
+      <c r="R1" s="6">
+        <v>46190</v>
+      </c>
+      <c r="S1" s="6">
+        <v>46191</v>
+      </c>
+      <c r="T1" s="6">
+        <v>46192</v>
+      </c>
+      <c r="U1" s="6">
+        <v>46193</v>
+      </c>
+      <c r="V1" s="6">
+        <v>46194</v>
+      </c>
+      <c r="W1" s="6">
+        <v>46195</v>
+      </c>
+      <c r="X1" s="6">
+        <v>46196</v>
+      </c>
+      <c r="Y1" s="6">
+        <v>46197</v>
+      </c>
+      <c r="Z1" s="6">
+        <v>46198</v>
+      </c>
+      <c r="AA1" s="6">
+        <v>46199</v>
+      </c>
+      <c r="AB1" s="6">
+        <v>46200</v>
+      </c>
+      <c r="AC1" s="6">
+        <v>46201</v>
+      </c>
+      <c r="AD1" s="6">
+        <v>46202</v>
+      </c>
+      <c r="AE1" s="6">
+        <v>46203</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C2" s="4">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D2" s="4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E2" s="4">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F2" s="4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G2" s="4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H2" s="4">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I2" s="4">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J2" s="4">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K2" s="4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L2" s="4">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="M2" s="4">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="N2" s="4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O2" s="4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P2" s="4">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="Q2" s="4">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="R2" s="4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S2" s="4">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="T2" s="4">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="U2" s="4">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="V2" s="4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="W2" s="4">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="X2" s="4">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="Y2" s="4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z2" s="4">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="AA2" s="4">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AB2" s="4">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AC2" s="4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AD2" s="4">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AE2" s="4">
-        <v>26</v>
-      </c>
-      <c r="AF2" s="4">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="4">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C3" s="4">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D3" s="4">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E3" s="4">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F3" s="4">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G3" s="4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H3" s="4">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I3" s="4">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J3" s="4">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K3" s="4">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L3" s="4">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="M3" s="4">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N3" s="4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O3" s="4">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P3" s="4">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="Q3" s="4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R3" s="4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S3" s="4">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T3" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U3" s="4">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="V3" s="4">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="W3" s="4">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="X3" s="4">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="Y3" s="4">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z3" s="4">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="AA3" s="4">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB3" s="4">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AC3" s="4">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AD3" s="4">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AE3" s="4">
-        <v>21</v>
-      </c>
-      <c r="AF3" s="4">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="4">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C4" s="4">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D4" s="4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E4" s="4">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F4" s="4">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G4" s="4">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H4" s="4">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I4" s="4">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J4" s="4">
+        <v>19</v>
+      </c>
+      <c r="K4" s="4">
+        <v>19</v>
+      </c>
+      <c r="L4" s="4">
+        <v>19</v>
+      </c>
+      <c r="M4" s="4">
+        <v>19</v>
+      </c>
+      <c r="N4" s="4">
+        <v>26</v>
+      </c>
+      <c r="O4" s="4">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>30</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>20</v>
+      </c>
+      <c r="R4" s="4">
+        <v>20</v>
+      </c>
+      <c r="S4" s="4">
+        <v>20</v>
+      </c>
+      <c r="T4" s="4">
+        <v>20</v>
+      </c>
+      <c r="U4" s="4">
+        <v>25</v>
+      </c>
+      <c r="V4" s="4">
+        <v>0</v>
+      </c>
+      <c r="W4" s="4">
         <v>29</v>
       </c>
-      <c r="K4" s="4">
-        <v>0</v>
-      </c>
-      <c r="L4" s="4">
-        <v>33</v>
-      </c>
-      <c r="M4" s="4">
-        <v>22</v>
-      </c>
-      <c r="N4" s="4">
-        <v>22</v>
-      </c>
-      <c r="O4" s="4">
-        <v>22</v>
-      </c>
-      <c r="P4" s="4">
-        <v>22</v>
-      </c>
-      <c r="Q4" s="4">
+      <c r="X4" s="4">
+        <v>19</v>
+      </c>
+      <c r="Y4" s="4">
+        <v>19</v>
+      </c>
+      <c r="Z4" s="4">
+        <v>19</v>
+      </c>
+      <c r="AA4" s="4">
+        <v>19</v>
+      </c>
+      <c r="AB4" s="4">
+        <v>25</v>
+      </c>
+      <c r="AC4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="4">
         <v>29</v>
       </c>
-      <c r="R4" s="4">
-        <v>0</v>
-      </c>
-      <c r="S4" s="4">
-        <v>33</v>
-      </c>
-      <c r="T4" s="4">
-        <v>22</v>
-      </c>
-      <c r="U4" s="4">
-        <v>22</v>
-      </c>
-      <c r="V4" s="4">
-        <v>22</v>
-      </c>
-      <c r="W4" s="4">
-        <v>22</v>
-      </c>
-      <c r="X4" s="4">
+      <c r="AE4" s="4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4">
+        <v>30</v>
+      </c>
+      <c r="C5" s="4">
+        <v>20</v>
+      </c>
+      <c r="D5" s="4">
+        <v>20</v>
+      </c>
+      <c r="E5" s="4">
+        <v>20</v>
+      </c>
+      <c r="F5" s="4">
+        <v>20</v>
+      </c>
+      <c r="G5" s="4">
+        <v>26</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
+        <v>30</v>
+      </c>
+      <c r="J5" s="4">
+        <v>20</v>
+      </c>
+      <c r="K5" s="4">
+        <v>20</v>
+      </c>
+      <c r="L5" s="4">
+        <v>20</v>
+      </c>
+      <c r="M5" s="4">
+        <v>20</v>
+      </c>
+      <c r="N5" s="4">
+        <v>26</v>
+      </c>
+      <c r="O5" s="4">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>30</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>20</v>
+      </c>
+      <c r="R5" s="4">
+        <v>20</v>
+      </c>
+      <c r="S5" s="4">
+        <v>20</v>
+      </c>
+      <c r="T5" s="4">
+        <v>20</v>
+      </c>
+      <c r="U5" s="4">
+        <v>25</v>
+      </c>
+      <c r="V5" s="4">
+        <v>0</v>
+      </c>
+      <c r="W5" s="4">
         <v>29</v>
       </c>
-      <c r="Y4" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="4">
-        <v>33</v>
-      </c>
-      <c r="AA4" s="4">
-        <v>22</v>
-      </c>
-      <c r="AB4" s="4">
-        <v>22</v>
-      </c>
-      <c r="AC4" s="4">
-        <v>22</v>
-      </c>
-      <c r="AD4" s="4">
-        <v>22</v>
-      </c>
-      <c r="AE4" s="4">
-        <v>28</v>
-      </c>
-      <c r="AF4" s="4">
-        <v>0</v>
+      <c r="X5" s="4">
+        <v>20</v>
+      </c>
+      <c r="Y5" s="4">
+        <v>20</v>
+      </c>
+      <c r="Z5" s="4">
+        <v>20</v>
+      </c>
+      <c r="AA5" s="4">
+        <v>20</v>
+      </c>
+      <c r="AB5" s="4">
+        <v>26</v>
+      </c>
+      <c r="AC5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="4">
+        <v>30</v>
+      </c>
+      <c r="AE5" s="4">
+        <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="A5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4">
-        <v>22</v>
-      </c>
-      <c r="C5" s="4">
-        <v>29</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4">
-        <v>33</v>
-      </c>
-      <c r="F5" s="4">
-        <v>22</v>
-      </c>
-      <c r="G5" s="4">
-        <v>22</v>
-      </c>
-      <c r="H5" s="4">
-        <v>22</v>
-      </c>
-      <c r="I5" s="4">
-        <v>22</v>
-      </c>
-      <c r="J5" s="4">
-        <v>29</v>
-      </c>
-      <c r="K5" s="4">
-        <v>0</v>
-      </c>
-      <c r="L5" s="4">
-        <v>33</v>
-      </c>
-      <c r="M5" s="4">
-        <v>22</v>
-      </c>
-      <c r="N5" s="4">
-        <v>22</v>
-      </c>
-      <c r="O5" s="4">
-        <v>22</v>
-      </c>
-      <c r="P5" s="4">
-        <v>23</v>
-      </c>
-      <c r="Q5" s="4">
-        <v>30</v>
-      </c>
-      <c r="R5" s="4">
-        <v>0</v>
-      </c>
-      <c r="S5" s="4">
-        <v>34</v>
-      </c>
-      <c r="T5" s="4">
-        <v>23</v>
-      </c>
-      <c r="U5" s="4">
-        <v>23</v>
-      </c>
-      <c r="V5" s="4">
-        <v>23</v>
-      </c>
-      <c r="W5" s="4">
-        <v>23</v>
-      </c>
-      <c r="X5" s="4">
-        <v>30</v>
-      </c>
-      <c r="Y5" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="4">
-        <v>34</v>
-      </c>
-      <c r="AA5" s="4">
-        <v>23</v>
-      </c>
-      <c r="AB5" s="4">
-        <v>23</v>
-      </c>
-      <c r="AC5" s="4">
-        <v>23</v>
-      </c>
-      <c r="AD5" s="4">
-        <v>22</v>
-      </c>
-      <c r="AE5" s="4">
-        <v>29</v>
-      </c>
-      <c r="AF5" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="4">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C6" s="4">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E6" s="4">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="F6" s="4">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G6" s="4">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H6" s="4">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I6" s="4">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="J6" s="4">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="K6" s="4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L6" s="4">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="M6" s="4">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="N6" s="4">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="O6" s="4">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="P6" s="4">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="Q6" s="4">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="R6" s="4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="S6" s="4">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="T6" s="4">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="U6" s="4">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="V6" s="4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W6" s="4">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="X6" s="4">
+        <v>24</v>
+      </c>
+      <c r="Y6" s="4">
+        <v>24</v>
+      </c>
+      <c r="Z6" s="4">
+        <v>24</v>
+      </c>
+      <c r="AA6" s="4">
+        <v>24</v>
+      </c>
+      <c r="AB6" s="4">
+        <v>31</v>
+      </c>
+      <c r="AC6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="4">
         <v>36</v>
       </c>
-      <c r="Y6" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="4">
-        <v>41</v>
-      </c>
-      <c r="AA6" s="4">
-        <v>28</v>
-      </c>
-      <c r="AB6" s="4">
-        <v>28</v>
-      </c>
-      <c r="AC6" s="4">
-        <v>28</v>
-      </c>
-      <c r="AD6" s="4">
-        <v>27</v>
-      </c>
       <c r="AE6" s="4">
-        <v>35</v>
-      </c>
-      <c r="AF6" s="4">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="4">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C7" s="4">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D7" s="4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E7" s="4">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F7" s="4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G7" s="4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H7" s="4">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I7" s="4">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J7" s="4">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K7" s="4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L7" s="4">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="M7" s="4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N7" s="4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="O7" s="4">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="P7" s="4">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="Q7" s="4">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R7" s="4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="S7" s="4">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="T7" s="4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="U7" s="4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="V7" s="4">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="W7" s="4">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="X7" s="4">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="Y7" s="4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z7" s="4">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="AA7" s="4">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AB7" s="4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AC7" s="4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AD7" s="4">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AE7" s="4">
-        <v>25</v>
-      </c>
-      <c r="AF7" s="4">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="4">
+        <v>22</v>
+      </c>
+      <c r="C8" s="4">
+        <v>14</v>
+      </c>
+      <c r="D8" s="4">
+        <v>14</v>
+      </c>
+      <c r="E8" s="4">
+        <v>14</v>
+      </c>
+      <c r="F8" s="4">
+        <v>14</v>
+      </c>
+      <c r="G8" s="4">
+        <v>19</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4">
+        <v>22</v>
+      </c>
+      <c r="J8" s="4">
+        <v>15</v>
+      </c>
+      <c r="K8" s="4">
+        <v>15</v>
+      </c>
+      <c r="L8" s="4">
+        <v>15</v>
+      </c>
+      <c r="M8" s="4">
+        <v>15</v>
+      </c>
+      <c r="N8" s="4">
+        <v>20</v>
+      </c>
+      <c r="O8" s="4">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4">
+        <v>23</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>15</v>
+      </c>
+      <c r="R8" s="4">
+        <v>15</v>
+      </c>
+      <c r="S8" s="4">
+        <v>15</v>
+      </c>
+      <c r="T8" s="4">
+        <v>15</v>
+      </c>
+      <c r="U8" s="4">
+        <v>19</v>
+      </c>
+      <c r="V8" s="4">
+        <v>0</v>
+      </c>
+      <c r="W8" s="4">
+        <v>22</v>
+      </c>
+      <c r="X8" s="4">
+        <v>15</v>
+      </c>
+      <c r="Y8" s="4">
+        <v>15</v>
+      </c>
+      <c r="Z8" s="4">
+        <v>15</v>
+      </c>
+      <c r="AA8" s="4">
+        <v>15</v>
+      </c>
+      <c r="AB8" s="4">
+        <v>19</v>
+      </c>
+      <c r="AC8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="4">
+        <v>22</v>
+      </c>
+      <c r="AE8" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4">
+        <v>25</v>
+      </c>
+      <c r="C9" s="4">
         <v>16</v>
       </c>
-      <c r="C8" s="4">
+      <c r="D9" s="4">
+        <v>16</v>
+      </c>
+      <c r="E9" s="4">
+        <v>16</v>
+      </c>
+      <c r="F9" s="4">
+        <v>16</v>
+      </c>
+      <c r="G9" s="4">
         <v>21</v>
       </c>
-      <c r="D8" s="4">
-        <v>0</v>
-      </c>
-      <c r="E8" s="4">
+      <c r="H9" s="4">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4">
         <v>25</v>
       </c>
-      <c r="F8" s="4">
+      <c r="J9" s="4">
         <v>16</v>
       </c>
-      <c r="G8" s="4">
+      <c r="K9" s="4">
         <v>16</v>
       </c>
-      <c r="H8" s="4">
+      <c r="L9" s="4">
         <v>16</v>
       </c>
-      <c r="I8" s="4">
+      <c r="M9" s="4">
         <v>16</v>
       </c>
-      <c r="J8" s="4">
+      <c r="N9" s="4">
         <v>21</v>
       </c>
-      <c r="K8" s="4">
-        <v>0</v>
-      </c>
-      <c r="L8" s="4">
+      <c r="O9" s="4">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4">
         <v>25</v>
       </c>
-      <c r="M8" s="4">
+      <c r="Q9" s="4">
         <v>16</v>
       </c>
-      <c r="N8" s="4">
-        <v>16</v>
-      </c>
-      <c r="O8" s="4">
-        <v>17</v>
-      </c>
-      <c r="P8" s="4">
-        <v>17</v>
-      </c>
-      <c r="Q8" s="4">
+      <c r="R9" s="4">
+        <v>17</v>
+      </c>
+      <c r="S9" s="4">
+        <v>17</v>
+      </c>
+      <c r="T9" s="4">
+        <v>17</v>
+      </c>
+      <c r="U9" s="4">
         <v>22</v>
       </c>
-      <c r="R8" s="4">
-        <v>0</v>
-      </c>
-      <c r="S8" s="4">
-        <v>26</v>
-      </c>
-      <c r="T8" s="4">
-        <v>17</v>
-      </c>
-      <c r="U8" s="4">
-        <v>17</v>
-      </c>
-      <c r="V8" s="4">
-        <v>17</v>
-      </c>
-      <c r="W8" s="4">
-        <v>17</v>
-      </c>
-      <c r="X8" s="4">
+      <c r="V9" s="4">
+        <v>0</v>
+      </c>
+      <c r="W9" s="4">
+        <v>25</v>
+      </c>
+      <c r="X9" s="4">
+        <v>17</v>
+      </c>
+      <c r="Y9" s="4">
+        <v>17</v>
+      </c>
+      <c r="Z9" s="4">
+        <v>17</v>
+      </c>
+      <c r="AA9" s="4">
+        <v>17</v>
+      </c>
+      <c r="AB9" s="4">
         <v>22</v>
       </c>
-      <c r="Y8" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="4">
-        <v>26</v>
-      </c>
-      <c r="AA8" s="4">
-        <v>17</v>
-      </c>
-      <c r="AB8" s="4">
-        <v>17</v>
-      </c>
-      <c r="AC8" s="4">
-        <v>17</v>
-      </c>
-      <c r="AD8" s="4">
-        <v>17</v>
-      </c>
-      <c r="AE8" s="4">
-        <v>22</v>
-      </c>
-      <c r="AF8" s="4">
-        <v>0</v>
+      <c r="AC9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="4">
+        <v>25</v>
+      </c>
+      <c r="AE9" s="4">
+        <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="A9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="4">
-        <v>18</v>
-      </c>
-      <c r="C9" s="4">
-        <v>24</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0</v>
-      </c>
-      <c r="E9" s="4">
-        <v>28</v>
-      </c>
-      <c r="F9" s="4">
-        <v>18</v>
-      </c>
-      <c r="G9" s="4">
-        <v>18</v>
-      </c>
-      <c r="H9" s="4">
-        <v>18</v>
-      </c>
-      <c r="I9" s="4">
-        <v>18</v>
-      </c>
-      <c r="J9" s="4">
-        <v>24</v>
-      </c>
-      <c r="K9" s="4">
-        <v>0</v>
-      </c>
-      <c r="L9" s="4">
-        <v>28</v>
-      </c>
-      <c r="M9" s="4">
-        <v>18</v>
-      </c>
-      <c r="N9" s="4">
-        <v>18</v>
-      </c>
-      <c r="O9" s="4">
-        <v>18</v>
-      </c>
-      <c r="P9" s="4">
-        <v>18</v>
-      </c>
-      <c r="Q9" s="4">
-        <v>25</v>
-      </c>
-      <c r="R9" s="4">
-        <v>0</v>
-      </c>
-      <c r="S9" s="4">
-        <v>29</v>
-      </c>
-      <c r="T9" s="4">
-        <v>19</v>
-      </c>
-      <c r="U9" s="4">
-        <v>19</v>
-      </c>
-      <c r="V9" s="4">
-        <v>19</v>
-      </c>
-      <c r="W9" s="4">
-        <v>19</v>
-      </c>
-      <c r="X9" s="4">
-        <v>25</v>
-      </c>
-      <c r="Y9" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="4">
-        <v>29</v>
-      </c>
-      <c r="AA9" s="4">
-        <v>19</v>
-      </c>
-      <c r="AB9" s="4">
-        <v>19</v>
-      </c>
-      <c r="AC9" s="4">
-        <v>19</v>
-      </c>
-      <c r="AD9" s="4">
-        <v>19</v>
-      </c>
-      <c r="AE9" s="4">
-        <v>24</v>
-      </c>
-      <c r="AF9" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="4">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C10" s="4">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D10" s="4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E10" s="4">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F10" s="4">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G10" s="4">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H10" s="4">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I10" s="4">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J10" s="4">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K10" s="4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L10" s="4">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="M10" s="4">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N10" s="4">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O10" s="4">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P10" s="4">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="Q10" s="4">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="R10" s="4">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S10" s="4">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="T10" s="4">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="U10" s="4">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="V10" s="4">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="W10" s="4">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="X10" s="4">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="Y10" s="4">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z10" s="4">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="AA10" s="4">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AB10" s="4">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AC10" s="4">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="4">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AE10" s="4">
-        <v>23</v>
-      </c>
-      <c r="AF10" s="4">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -2143,812 +2116,788 @@
   <sheetPr>
     <tabColor theme="1"/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AE10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="32" width="5.75" style="1" customWidth="1"/>
-    <col min="33" max="16384" width="9" style="1"/>
+    <col min="1" max="31" width="5.75" style="1" customWidth="1"/>
+    <col min="32" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="2">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="C1" s="2">
-        <v>46144</v>
+        <v>46175</v>
       </c>
       <c r="D1" s="2">
-        <v>46145</v>
+        <v>46176</v>
       </c>
       <c r="E1" s="2">
-        <v>46146</v>
+        <v>46177</v>
       </c>
       <c r="F1" s="2">
-        <v>46147</v>
+        <v>46178</v>
       </c>
       <c r="G1" s="2">
-        <v>46148</v>
+        <v>46179</v>
       </c>
       <c r="H1" s="2">
-        <v>46149</v>
+        <v>46180</v>
       </c>
       <c r="I1" s="2">
-        <v>46150</v>
+        <v>46181</v>
       </c>
       <c r="J1" s="2">
-        <v>46151</v>
+        <v>46182</v>
       </c>
       <c r="K1" s="2">
-        <v>46152</v>
+        <v>46183</v>
       </c>
       <c r="L1" s="2">
-        <v>46153</v>
+        <v>46184</v>
       </c>
       <c r="M1" s="2">
-        <v>46154</v>
+        <v>46185</v>
       </c>
       <c r="N1" s="2">
-        <v>46155</v>
+        <v>46186</v>
       </c>
       <c r="O1" s="2">
-        <v>46156</v>
+        <v>46187</v>
       </c>
       <c r="P1" s="2">
-        <v>46157</v>
+        <v>46188</v>
       </c>
       <c r="Q1" s="2">
-        <v>46158</v>
+        <v>46189</v>
       </c>
       <c r="R1" s="2">
-        <v>46159</v>
+        <v>46190</v>
       </c>
       <c r="S1" s="2">
-        <v>46160</v>
+        <v>46191</v>
       </c>
       <c r="T1" s="2">
-        <v>46161</v>
+        <v>46192</v>
       </c>
       <c r="U1" s="2">
-        <v>46162</v>
+        <v>46193</v>
       </c>
       <c r="V1" s="2">
-        <v>46163</v>
+        <v>46194</v>
       </c>
       <c r="W1" s="2">
-        <v>46164</v>
+        <v>46195</v>
       </c>
       <c r="X1" s="2">
-        <v>46165</v>
+        <v>46196</v>
       </c>
       <c r="Y1" s="2">
-        <v>46166</v>
+        <v>46197</v>
       </c>
       <c r="Z1" s="2">
-        <v>46167</v>
+        <v>46198</v>
       </c>
       <c r="AA1" s="2">
-        <v>46168</v>
+        <v>46199</v>
       </c>
       <c r="AB1" s="2">
-        <v>46169</v>
+        <v>46200</v>
       </c>
       <c r="AC1" s="2">
-        <v>46170</v>
+        <v>46201</v>
       </c>
       <c r="AD1" s="2">
-        <v>46171</v>
+        <v>46202</v>
       </c>
       <c r="AE1" s="2">
-        <v>46172</v>
-      </c>
-      <c r="AF1" s="2">
-        <v>46173</v>
+        <v>46203</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="4">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4">
+        <v>4</v>
+      </c>
+      <c r="F2" s="4">
+        <v>4</v>
+      </c>
+      <c r="G2" s="4">
+        <v>5</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
         <v>6</v>
       </c>
-      <c r="D2" s="4">
-        <v>0</v>
-      </c>
-      <c r="E2" s="4">
+      <c r="J2" s="4">
+        <v>4</v>
+      </c>
+      <c r="K2" s="4">
+        <v>4</v>
+      </c>
+      <c r="L2" s="4">
+        <v>4</v>
+      </c>
+      <c r="M2" s="4">
+        <v>4</v>
+      </c>
+      <c r="N2" s="4">
+        <v>5</v>
+      </c>
+      <c r="O2" s="4">
+        <v>0</v>
+      </c>
+      <c r="P2" s="4">
+        <v>6</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>4</v>
+      </c>
+      <c r="R2" s="4">
+        <v>4</v>
+      </c>
+      <c r="S2" s="4">
+        <v>4</v>
+      </c>
+      <c r="T2" s="4">
+        <v>4</v>
+      </c>
+      <c r="U2" s="4">
+        <v>5</v>
+      </c>
+      <c r="V2" s="4">
+        <v>0</v>
+      </c>
+      <c r="W2" s="4">
+        <v>6</v>
+      </c>
+      <c r="X2" s="4">
+        <v>4</v>
+      </c>
+      <c r="Y2" s="4">
+        <v>4</v>
+      </c>
+      <c r="Z2" s="4">
+        <v>4</v>
+      </c>
+      <c r="AA2" s="4">
+        <v>5</v>
+      </c>
+      <c r="AB2" s="4">
+        <v>6</v>
+      </c>
+      <c r="AC2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="4">
         <v>7</v>
       </c>
-      <c r="F2" s="4">
-        <v>5</v>
-      </c>
-      <c r="G2" s="4">
-        <v>5</v>
-      </c>
-      <c r="H2" s="4">
-        <v>5</v>
-      </c>
-      <c r="I2" s="4">
-        <v>5</v>
-      </c>
-      <c r="J2" s="4">
-        <v>6</v>
-      </c>
-      <c r="K2" s="4">
-        <v>0</v>
-      </c>
-      <c r="L2" s="4">
-        <v>7</v>
-      </c>
-      <c r="M2" s="4">
-        <v>5</v>
-      </c>
-      <c r="N2" s="4">
-        <v>5</v>
-      </c>
-      <c r="O2" s="4">
-        <v>5</v>
-      </c>
-      <c r="P2" s="4">
-        <v>5</v>
-      </c>
-      <c r="Q2" s="4">
-        <v>6</v>
-      </c>
-      <c r="R2" s="4">
-        <v>0</v>
-      </c>
-      <c r="S2" s="4">
-        <v>7</v>
-      </c>
-      <c r="T2" s="4">
-        <v>5</v>
-      </c>
-      <c r="U2" s="4">
-        <v>5</v>
-      </c>
-      <c r="V2" s="4">
-        <v>5</v>
-      </c>
-      <c r="W2" s="4">
-        <v>5</v>
-      </c>
-      <c r="X2" s="4">
-        <v>6</v>
-      </c>
-      <c r="Y2" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="4">
-        <v>7</v>
-      </c>
-      <c r="AA2" s="4">
-        <v>5</v>
-      </c>
-      <c r="AB2" s="4">
-        <v>5</v>
-      </c>
-      <c r="AC2" s="4">
-        <v>6</v>
-      </c>
-      <c r="AD2" s="4">
-        <v>6</v>
-      </c>
       <c r="AE2" s="4">
-        <v>7</v>
-      </c>
-      <c r="AF2" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D3" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E3" s="4">
+        <v>3</v>
+      </c>
+      <c r="F3" s="4">
+        <v>3</v>
+      </c>
+      <c r="G3" s="4">
+        <v>4</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>5</v>
+      </c>
+      <c r="J3" s="4">
+        <v>3</v>
+      </c>
+      <c r="K3" s="4">
+        <v>3</v>
+      </c>
+      <c r="L3" s="4">
+        <v>3</v>
+      </c>
+      <c r="M3" s="4">
+        <v>3</v>
+      </c>
+      <c r="N3" s="4">
+        <v>4</v>
+      </c>
+      <c r="O3" s="4">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>3</v>
+      </c>
+      <c r="R3" s="4">
+        <v>3</v>
+      </c>
+      <c r="S3" s="4">
+        <v>3</v>
+      </c>
+      <c r="T3" s="4">
+        <v>4</v>
+      </c>
+      <c r="U3" s="4">
+        <v>5</v>
+      </c>
+      <c r="V3" s="4">
+        <v>0</v>
+      </c>
+      <c r="W3" s="4">
         <v>6</v>
       </c>
-      <c r="F3" s="4">
-        <v>4</v>
-      </c>
-      <c r="G3" s="4">
-        <v>4</v>
-      </c>
-      <c r="H3" s="4">
-        <v>4</v>
-      </c>
-      <c r="I3" s="4">
-        <v>4</v>
-      </c>
-      <c r="J3" s="4">
-        <v>5</v>
-      </c>
-      <c r="K3" s="4">
-        <v>0</v>
-      </c>
-      <c r="L3" s="4">
+      <c r="X3" s="4">
+        <v>4</v>
+      </c>
+      <c r="Y3" s="4">
+        <v>4</v>
+      </c>
+      <c r="Z3" s="4">
+        <v>4</v>
+      </c>
+      <c r="AA3" s="4">
+        <v>4</v>
+      </c>
+      <c r="AB3" s="4">
+        <v>5</v>
+      </c>
+      <c r="AC3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="4">
         <v>6</v>
       </c>
-      <c r="M3" s="4">
-        <v>4</v>
-      </c>
-      <c r="N3" s="4">
-        <v>4</v>
-      </c>
-      <c r="O3" s="4">
-        <v>4</v>
-      </c>
-      <c r="P3" s="4">
-        <v>4</v>
-      </c>
-      <c r="Q3" s="4">
-        <v>5</v>
-      </c>
-      <c r="R3" s="4">
-        <v>0</v>
-      </c>
-      <c r="S3" s="4">
-        <v>6</v>
-      </c>
-      <c r="T3" s="4">
-        <v>4</v>
-      </c>
-      <c r="U3" s="4">
-        <v>4</v>
-      </c>
-      <c r="V3" s="4">
-        <v>4</v>
-      </c>
-      <c r="W3" s="4">
-        <v>4</v>
-      </c>
-      <c r="X3" s="4">
-        <v>5</v>
-      </c>
-      <c r="Y3" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="4">
-        <v>6</v>
-      </c>
-      <c r="AA3" s="4">
-        <v>5</v>
-      </c>
-      <c r="AB3" s="4">
-        <v>5</v>
-      </c>
-      <c r="AC3" s="4">
-        <v>5</v>
-      </c>
-      <c r="AD3" s="4">
-        <v>5</v>
-      </c>
       <c r="AE3" s="4">
-        <v>6</v>
-      </c>
-      <c r="AF3" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="4">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4">
+        <v>4</v>
+      </c>
+      <c r="E4" s="4">
+        <v>4</v>
+      </c>
+      <c r="F4" s="4">
+        <v>4</v>
+      </c>
+      <c r="G4" s="4">
+        <v>5</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
+        <v>5</v>
+      </c>
+      <c r="J4" s="4">
+        <v>4</v>
+      </c>
+      <c r="K4" s="4">
+        <v>4</v>
+      </c>
+      <c r="L4" s="4">
+        <v>4</v>
+      </c>
+      <c r="M4" s="4">
+        <v>4</v>
+      </c>
+      <c r="N4" s="4">
+        <v>5</v>
+      </c>
+      <c r="O4" s="4">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>4</v>
+      </c>
+      <c r="R4" s="4">
+        <v>4</v>
+      </c>
+      <c r="S4" s="4">
+        <v>4</v>
+      </c>
+      <c r="T4" s="4">
+        <v>4</v>
+      </c>
+      <c r="U4" s="4">
+        <v>5</v>
+      </c>
+      <c r="V4" s="4">
+        <v>0</v>
+      </c>
+      <c r="W4" s="4">
+        <v>5</v>
+      </c>
+      <c r="X4" s="4">
+        <v>4</v>
+      </c>
+      <c r="Y4" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z4" s="4">
+        <v>3</v>
+      </c>
+      <c r="AA4" s="4">
+        <v>3</v>
+      </c>
+      <c r="AB4" s="4">
+        <v>4</v>
+      </c>
+      <c r="AC4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="4">
+        <v>4</v>
+      </c>
+      <c r="AE4" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4">
         <v>6</v>
       </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="4">
-        <v>7</v>
-      </c>
-      <c r="F4" s="4">
-        <v>4</v>
-      </c>
-      <c r="G4" s="4">
-        <v>4</v>
-      </c>
-      <c r="H4" s="4">
-        <v>4</v>
-      </c>
-      <c r="I4" s="4">
-        <v>4</v>
-      </c>
-      <c r="J4" s="4">
+      <c r="C5" s="4">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4">
+        <v>4</v>
+      </c>
+      <c r="E5" s="4">
+        <v>4</v>
+      </c>
+      <c r="F5" s="4">
+        <v>4</v>
+      </c>
+      <c r="G5" s="4">
+        <v>5</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
         <v>6</v>
       </c>
-      <c r="K4" s="4">
-        <v>0</v>
-      </c>
-      <c r="L4" s="4">
-        <v>7</v>
-      </c>
-      <c r="M4" s="4">
-        <v>4</v>
-      </c>
-      <c r="N4" s="4">
-        <v>4</v>
-      </c>
-      <c r="O4" s="4">
-        <v>4</v>
-      </c>
-      <c r="P4" s="4">
-        <v>4</v>
-      </c>
-      <c r="Q4" s="4">
+      <c r="J5" s="4">
+        <v>4</v>
+      </c>
+      <c r="K5" s="4">
+        <v>4</v>
+      </c>
+      <c r="L5" s="4">
+        <v>4</v>
+      </c>
+      <c r="M5" s="4">
+        <v>4</v>
+      </c>
+      <c r="N5" s="4">
+        <v>5</v>
+      </c>
+      <c r="O5" s="4">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
         <v>6</v>
       </c>
-      <c r="R4" s="4">
-        <v>0</v>
-      </c>
-      <c r="S4" s="4">
-        <v>7</v>
-      </c>
-      <c r="T4" s="4">
-        <v>4</v>
-      </c>
-      <c r="U4" s="4">
-        <v>4</v>
-      </c>
-      <c r="V4" s="4">
-        <v>4</v>
-      </c>
-      <c r="W4" s="4">
-        <v>4</v>
-      </c>
-      <c r="X4" s="4">
+      <c r="Q5" s="4">
+        <v>4</v>
+      </c>
+      <c r="R5" s="4">
+        <v>4</v>
+      </c>
+      <c r="S5" s="4">
+        <v>4</v>
+      </c>
+      <c r="T5" s="4">
+        <v>4</v>
+      </c>
+      <c r="U5" s="4">
+        <v>5</v>
+      </c>
+      <c r="V5" s="4">
+        <v>0</v>
+      </c>
+      <c r="W5" s="4">
         <v>6</v>
       </c>
-      <c r="Y4" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="4">
-        <v>7</v>
-      </c>
-      <c r="AA4" s="4">
-        <v>4</v>
-      </c>
-      <c r="AB4" s="4">
-        <v>4</v>
-      </c>
-      <c r="AC4" s="4">
-        <v>5</v>
-      </c>
-      <c r="AD4" s="4">
-        <v>5</v>
-      </c>
-      <c r="AE4" s="4">
-        <v>7</v>
-      </c>
-      <c r="AF4" s="4">
-        <v>0</v>
+      <c r="X5" s="4">
+        <v>4</v>
+      </c>
+      <c r="Y5" s="4">
+        <v>4</v>
+      </c>
+      <c r="Z5" s="4">
+        <v>3</v>
+      </c>
+      <c r="AA5" s="4">
+        <v>3</v>
+      </c>
+      <c r="AB5" s="4">
+        <v>4</v>
+      </c>
+      <c r="AC5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="4">
+        <v>5</v>
+      </c>
+      <c r="AE5" s="4">
+        <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="A5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4">
-        <v>5</v>
-      </c>
-      <c r="C5" s="4">
-        <v>6</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4">
-        <v>7</v>
-      </c>
-      <c r="F5" s="4">
-        <v>5</v>
-      </c>
-      <c r="G5" s="4">
-        <v>5</v>
-      </c>
-      <c r="H5" s="4">
-        <v>5</v>
-      </c>
-      <c r="I5" s="4">
-        <v>5</v>
-      </c>
-      <c r="J5" s="4">
-        <v>6</v>
-      </c>
-      <c r="K5" s="4">
-        <v>0</v>
-      </c>
-      <c r="L5" s="4">
-        <v>7</v>
-      </c>
-      <c r="M5" s="4">
-        <v>5</v>
-      </c>
-      <c r="N5" s="4">
-        <v>5</v>
-      </c>
-      <c r="O5" s="4">
-        <v>5</v>
-      </c>
-      <c r="P5" s="4">
-        <v>5</v>
-      </c>
-      <c r="Q5" s="4">
-        <v>6</v>
-      </c>
-      <c r="R5" s="4">
-        <v>0</v>
-      </c>
-      <c r="S5" s="4">
-        <v>7</v>
-      </c>
-      <c r="T5" s="4">
-        <v>5</v>
-      </c>
-      <c r="U5" s="4">
-        <v>5</v>
-      </c>
-      <c r="V5" s="4">
-        <v>5</v>
-      </c>
-      <c r="W5" s="4">
-        <v>5</v>
-      </c>
-      <c r="X5" s="4">
-        <v>6</v>
-      </c>
-      <c r="Y5" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="4">
-        <v>6</v>
-      </c>
-      <c r="AA5" s="4">
-        <v>4</v>
-      </c>
-      <c r="AB5" s="4">
-        <v>4</v>
-      </c>
-      <c r="AC5" s="4">
-        <v>4</v>
-      </c>
-      <c r="AD5" s="4">
-        <v>3</v>
-      </c>
-      <c r="AE5" s="4">
-        <v>5</v>
-      </c>
-      <c r="AF5" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D6" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E6" s="4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F6" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G6" s="4">
         <v>6</v>
       </c>
       <c r="H6" s="4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I6" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J6" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K6" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L6" s="4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M6" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N6" s="4">
         <v>6</v>
       </c>
       <c r="O6" s="4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P6" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q6" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R6" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S6" s="4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T6" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U6" s="4">
         <v>6</v>
       </c>
       <c r="V6" s="4">
+        <v>0</v>
+      </c>
+      <c r="W6" s="4">
+        <v>7</v>
+      </c>
+      <c r="X6" s="4">
+        <v>5</v>
+      </c>
+      <c r="Y6" s="4">
+        <v>5</v>
+      </c>
+      <c r="Z6" s="4">
+        <v>5</v>
+      </c>
+      <c r="AA6" s="4">
+        <v>5</v>
+      </c>
+      <c r="AB6" s="4">
+        <v>5</v>
+      </c>
+      <c r="AC6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="4">
         <v>6</v>
       </c>
-      <c r="W6" s="4">
+      <c r="AE6" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
+      <c r="A7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4">
         <v>6</v>
       </c>
-      <c r="X6" s="4">
-        <v>7</v>
-      </c>
-      <c r="Y6" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="4">
-        <v>9</v>
-      </c>
-      <c r="AA6" s="4">
+      <c r="C7" s="4">
+        <v>4</v>
+      </c>
+      <c r="D7" s="4">
+        <v>4</v>
+      </c>
+      <c r="E7" s="4">
+        <v>4</v>
+      </c>
+      <c r="F7" s="4">
+        <v>4</v>
+      </c>
+      <c r="G7" s="4">
+        <v>5</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4">
         <v>6</v>
       </c>
-      <c r="AB6" s="4">
-        <v>5</v>
-      </c>
-      <c r="AC6" s="4">
-        <v>5</v>
-      </c>
-      <c r="AD6" s="4">
-        <v>5</v>
-      </c>
-      <c r="AE6" s="4">
+      <c r="J7" s="4">
+        <v>4</v>
+      </c>
+      <c r="K7" s="4">
+        <v>4</v>
+      </c>
+      <c r="L7" s="4">
+        <v>4</v>
+      </c>
+      <c r="M7" s="4">
+        <v>4</v>
+      </c>
+      <c r="N7" s="4">
+        <v>5</v>
+      </c>
+      <c r="O7" s="4">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4">
         <v>6</v>
       </c>
-      <c r="AF6" s="4">
-        <v>0</v>
+      <c r="Q7" s="4">
+        <v>4</v>
+      </c>
+      <c r="R7" s="4">
+        <v>4</v>
+      </c>
+      <c r="S7" s="4">
+        <v>4</v>
+      </c>
+      <c r="T7" s="4">
+        <v>4</v>
+      </c>
+      <c r="U7" s="4">
+        <v>5</v>
+      </c>
+      <c r="V7" s="4">
+        <v>0</v>
+      </c>
+      <c r="W7" s="4">
+        <v>5</v>
+      </c>
+      <c r="X7" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y7" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z7" s="4">
+        <v>3</v>
+      </c>
+      <c r="AA7" s="4">
+        <v>3</v>
+      </c>
+      <c r="AB7" s="4">
+        <v>4</v>
+      </c>
+      <c r="AC7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="4">
+        <v>5</v>
+      </c>
+      <c r="AE7" s="4">
+        <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="A7" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4">
-        <v>4</v>
-      </c>
-      <c r="C7" s="4">
-        <v>6</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="4">
-        <v>7</v>
-      </c>
-      <c r="F7" s="4">
-        <v>4</v>
-      </c>
-      <c r="G7" s="4">
-        <v>4</v>
-      </c>
-      <c r="H7" s="4">
-        <v>4</v>
-      </c>
-      <c r="I7" s="4">
-        <v>4</v>
-      </c>
-      <c r="J7" s="4">
-        <v>6</v>
-      </c>
-      <c r="K7" s="4">
-        <v>0</v>
-      </c>
-      <c r="L7" s="4">
-        <v>7</v>
-      </c>
-      <c r="M7" s="4">
-        <v>4</v>
-      </c>
-      <c r="N7" s="4">
-        <v>4</v>
-      </c>
-      <c r="O7" s="4">
-        <v>4</v>
-      </c>
-      <c r="P7" s="4">
-        <v>4</v>
-      </c>
-      <c r="Q7" s="4">
-        <v>6</v>
-      </c>
-      <c r="R7" s="4">
-        <v>0</v>
-      </c>
-      <c r="S7" s="4">
-        <v>7</v>
-      </c>
-      <c r="T7" s="4">
-        <v>4</v>
-      </c>
-      <c r="U7" s="4">
-        <v>4</v>
-      </c>
-      <c r="V7" s="4">
-        <v>4</v>
-      </c>
-      <c r="W7" s="4">
-        <v>4</v>
-      </c>
-      <c r="X7" s="4">
-        <v>6</v>
-      </c>
-      <c r="Y7" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="4">
-        <v>8</v>
-      </c>
-      <c r="AA7" s="4">
-        <v>5</v>
-      </c>
-      <c r="AB7" s="4">
-        <v>5</v>
-      </c>
-      <c r="AC7" s="4">
-        <v>5</v>
-      </c>
-      <c r="AD7" s="4">
-        <v>5</v>
-      </c>
-      <c r="AE7" s="4">
-        <v>7</v>
-      </c>
-      <c r="AF7" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D8" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E8" s="4">
+        <v>3</v>
+      </c>
+      <c r="F8" s="4">
+        <v>3</v>
+      </c>
+      <c r="G8" s="4">
+        <v>4</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4">
+        <v>5</v>
+      </c>
+      <c r="J8" s="4">
+        <v>3</v>
+      </c>
+      <c r="K8" s="4">
+        <v>3</v>
+      </c>
+      <c r="L8" s="4">
+        <v>3</v>
+      </c>
+      <c r="M8" s="4">
+        <v>3</v>
+      </c>
+      <c r="N8" s="4">
+        <v>4</v>
+      </c>
+      <c r="O8" s="4">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>3</v>
+      </c>
+      <c r="R8" s="4">
+        <v>3</v>
+      </c>
+      <c r="S8" s="4">
+        <v>3</v>
+      </c>
+      <c r="T8" s="4">
+        <v>3</v>
+      </c>
+      <c r="U8" s="4">
+        <v>4</v>
+      </c>
+      <c r="V8" s="4">
+        <v>0</v>
+      </c>
+      <c r="W8" s="4">
+        <v>5</v>
+      </c>
+      <c r="X8" s="4">
+        <v>4</v>
+      </c>
+      <c r="Y8" s="4">
+        <v>4</v>
+      </c>
+      <c r="Z8" s="4">
+        <v>4</v>
+      </c>
+      <c r="AA8" s="4">
+        <v>4</v>
+      </c>
+      <c r="AB8" s="4">
+        <v>5</v>
+      </c>
+      <c r="AC8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="4">
         <v>6</v>
       </c>
-      <c r="F8" s="4">
-        <v>4</v>
-      </c>
-      <c r="G8" s="4">
-        <v>4</v>
-      </c>
-      <c r="H8" s="4">
-        <v>4</v>
-      </c>
-      <c r="I8" s="4">
-        <v>4</v>
-      </c>
-      <c r="J8" s="4">
-        <v>5</v>
-      </c>
-      <c r="K8" s="4">
-        <v>0</v>
-      </c>
-      <c r="L8" s="4">
-        <v>6</v>
-      </c>
-      <c r="M8" s="4">
-        <v>4</v>
-      </c>
-      <c r="N8" s="4">
-        <v>4</v>
-      </c>
-      <c r="O8" s="4">
-        <v>4</v>
-      </c>
-      <c r="P8" s="4">
-        <v>4</v>
-      </c>
-      <c r="Q8" s="4">
-        <v>5</v>
-      </c>
-      <c r="R8" s="4">
-        <v>0</v>
-      </c>
-      <c r="S8" s="4">
-        <v>6</v>
-      </c>
-      <c r="T8" s="4">
-        <v>4</v>
-      </c>
-      <c r="U8" s="4">
-        <v>4</v>
-      </c>
-      <c r="V8" s="4">
-        <v>4</v>
-      </c>
-      <c r="W8" s="4">
-        <v>4</v>
-      </c>
-      <c r="X8" s="4">
-        <v>5</v>
-      </c>
-      <c r="Y8" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="4">
-        <v>6</v>
-      </c>
-      <c r="AA8" s="4">
-        <v>4</v>
-      </c>
-      <c r="AB8" s="4">
-        <v>4</v>
-      </c>
-      <c r="AC8" s="4">
-        <v>4</v>
-      </c>
-      <c r="AD8" s="4">
-        <v>5</v>
-      </c>
       <c r="AE8" s="4">
-        <v>6</v>
-      </c>
-      <c r="AF8" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B9" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E9" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F9" s="4">
         <v>3</v>
@@ -2957,19 +2906,19 @@
         <v>3</v>
       </c>
       <c r="H9" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I9" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K9" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M9" s="4">
         <v>3</v>
@@ -2978,19 +2927,19 @@
         <v>3</v>
       </c>
       <c r="O9" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P9" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q9" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R9" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S9" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T9" s="4">
         <v>3</v>
@@ -2999,135 +2948,129 @@
         <v>3</v>
       </c>
       <c r="V9" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W9" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X9" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y9" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z9" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AA9" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB9" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC9" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD9" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE9" s="4">
-        <v>5</v>
-      </c>
-      <c r="AF9" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D10" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E10" s="4">
+        <v>3</v>
+      </c>
+      <c r="F10" s="4">
+        <v>3</v>
+      </c>
+      <c r="G10" s="4">
+        <v>4</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4">
+        <v>5</v>
+      </c>
+      <c r="J10" s="4">
+        <v>3</v>
+      </c>
+      <c r="K10" s="4">
+        <v>3</v>
+      </c>
+      <c r="L10" s="4">
+        <v>3</v>
+      </c>
+      <c r="M10" s="4">
+        <v>3</v>
+      </c>
+      <c r="N10" s="4">
+        <v>4</v>
+      </c>
+      <c r="O10" s="4">
+        <v>0</v>
+      </c>
+      <c r="P10" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>3</v>
+      </c>
+      <c r="R10" s="4">
+        <v>3</v>
+      </c>
+      <c r="S10" s="4">
+        <v>3</v>
+      </c>
+      <c r="T10" s="4">
+        <v>4</v>
+      </c>
+      <c r="U10" s="4">
+        <v>5</v>
+      </c>
+      <c r="V10" s="4">
+        <v>0</v>
+      </c>
+      <c r="W10" s="4">
         <v>6</v>
       </c>
-      <c r="F10" s="4">
-        <v>4</v>
-      </c>
-      <c r="G10" s="4">
-        <v>4</v>
-      </c>
-      <c r="H10" s="4">
-        <v>4</v>
-      </c>
-      <c r="I10" s="4">
-        <v>4</v>
-      </c>
-      <c r="J10" s="4">
-        <v>5</v>
-      </c>
-      <c r="K10" s="4">
-        <v>0</v>
-      </c>
-      <c r="L10" s="4">
+      <c r="X10" s="4">
+        <v>4</v>
+      </c>
+      <c r="Y10" s="4">
+        <v>4</v>
+      </c>
+      <c r="Z10" s="4">
+        <v>4</v>
+      </c>
+      <c r="AA10" s="4">
+        <v>4</v>
+      </c>
+      <c r="AB10" s="4">
+        <v>5</v>
+      </c>
+      <c r="AC10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="4">
         <v>6</v>
       </c>
-      <c r="M10" s="4">
-        <v>4</v>
-      </c>
-      <c r="N10" s="4">
-        <v>4</v>
-      </c>
-      <c r="O10" s="4">
-        <v>4</v>
-      </c>
-      <c r="P10" s="4">
-        <v>4</v>
-      </c>
-      <c r="Q10" s="4">
-        <v>5</v>
-      </c>
-      <c r="R10" s="4">
-        <v>0</v>
-      </c>
-      <c r="S10" s="4">
-        <v>6</v>
-      </c>
-      <c r="T10" s="4">
-        <v>4</v>
-      </c>
-      <c r="U10" s="4">
-        <v>4</v>
-      </c>
-      <c r="V10" s="4">
-        <v>4</v>
-      </c>
-      <c r="W10" s="4">
-        <v>4</v>
-      </c>
-      <c r="X10" s="4">
-        <v>5</v>
-      </c>
-      <c r="Y10" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="4">
-        <v>6</v>
-      </c>
-      <c r="AA10" s="4">
-        <v>5</v>
-      </c>
-      <c r="AB10" s="4">
-        <v>5</v>
-      </c>
-      <c r="AC10" s="4">
-        <v>5</v>
-      </c>
-      <c r="AD10" s="4">
-        <v>5</v>
-      </c>
       <c r="AE10" s="4">
-        <v>6</v>
-      </c>
-      <c r="AF10" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/target.xlsx
+++ b/target.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\백업폴더\딱따구리\AI\강북도매 영업관리 포털\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F575D52-7364-4D52-9137-4A2F9B3F4967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A1BBBF1-E804-4D1D-A66D-135D7038EA62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F51F585E-D8DA-4EE1-A615-D4BBA305B88C}"/>
   </bookViews>
@@ -1296,7 +1296,7 @@
         <v>0</v>
       </c>
       <c r="P2" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q2" s="4">
         <v>18</v>
@@ -1317,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="W2" s="4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="X2" s="4">
         <v>18</v>
@@ -1338,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="AD2" s="4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE2" s="4">
         <v>18</v>
@@ -1394,7 +1394,7 @@
         <v>21</v>
       </c>
       <c r="Q3" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R3" s="4">
         <v>15</v>
@@ -1510,16 +1510,16 @@
         <v>29</v>
       </c>
       <c r="X4" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y4" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z4" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA4" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB4" s="4">
         <v>25</v>
@@ -1531,7 +1531,7 @@
         <v>29</v>
       </c>
       <c r="AE4" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.45">
@@ -1539,22 +1539,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5" s="4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5" s="4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E5" s="4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F5" s="4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G5" s="4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H5" s="4">
         <v>0</v>
@@ -1596,13 +1596,13 @@
         <v>20</v>
       </c>
       <c r="U5" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="V5" s="4">
         <v>0</v>
       </c>
       <c r="W5" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X5" s="4">
         <v>20</v>
@@ -1676,10 +1676,10 @@
         <v>0</v>
       </c>
       <c r="P6" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R6" s="4">
         <v>25</v>
@@ -1691,13 +1691,13 @@
         <v>25</v>
       </c>
       <c r="U6" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="V6" s="4">
         <v>0</v>
       </c>
       <c r="W6" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X6" s="4">
         <v>24</v>
@@ -1712,13 +1712,13 @@
         <v>24</v>
       </c>
       <c r="AB6" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AC6" s="4">
         <v>0</v>
       </c>
       <c r="AD6" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AE6" s="4">
         <v>24</v>
@@ -1732,19 +1732,19 @@
         <v>25</v>
       </c>
       <c r="C7" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E7" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F7" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G7" s="4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H7" s="4">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="P7" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q7" s="4">
         <v>17</v>
@@ -1786,7 +1786,7 @@
         <v>17</v>
       </c>
       <c r="U7" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V7" s="4">
         <v>0</v>
@@ -1795,7 +1795,7 @@
         <v>25</v>
       </c>
       <c r="X7" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y7" s="4">
         <v>17</v>
@@ -1813,7 +1813,7 @@
         <v>0</v>
       </c>
       <c r="AD7" s="4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE7" s="4">
         <v>17</v>
@@ -1848,10 +1848,10 @@
         <v>22</v>
       </c>
       <c r="J8" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K8" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L8" s="4">
         <v>15</v>
@@ -1955,16 +1955,16 @@
         <v>16</v>
       </c>
       <c r="N9" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O9" s="4">
         <v>0</v>
       </c>
       <c r="P9" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q9" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R9" s="4">
         <v>17</v>
@@ -2047,7 +2047,7 @@
         <v>15</v>
       </c>
       <c r="M10" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N10" s="4">
         <v>21</v>
@@ -2071,7 +2071,7 @@
         <v>16</v>
       </c>
       <c r="U10" s="4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V10" s="4">
         <v>0</v>
@@ -2092,7 +2092,7 @@
         <v>16</v>
       </c>
       <c r="AB10" s="4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC10" s="4">
         <v>0</v>
@@ -2298,10 +2298,10 @@
         <v>4</v>
       </c>
       <c r="AA2" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB2" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC2" s="4">
         <v>0</v>
@@ -2321,19 +2321,19 @@
         <v>5</v>
       </c>
       <c r="C3" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3" s="4">
         <v>0</v>
@@ -2342,19 +2342,19 @@
         <v>5</v>
       </c>
       <c r="J3" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L3" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M3" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N3" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O3" s="4">
         <v>0</v>
@@ -2363,49 +2363,49 @@
         <v>5</v>
       </c>
       <c r="Q3" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R3" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S3" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" s="4">
         <v>4</v>
       </c>
       <c r="U3" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V3" s="4">
         <v>0</v>
       </c>
       <c r="W3" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X3" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y3" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z3" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA3" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB3" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AC3" s="4">
         <v>0</v>
       </c>
       <c r="AD3" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE3" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.45">
@@ -2413,7 +2413,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="4">
         <v>4</v>
@@ -2434,7 +2434,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J4" s="4">
         <v>4</v>
@@ -2455,7 +2455,7 @@
         <v>0</v>
       </c>
       <c r="P4" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q4" s="4">
         <v>4</v>
@@ -2476,10 +2476,10 @@
         <v>0</v>
       </c>
       <c r="W4" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X4" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y4" s="4">
         <v>3</v>
@@ -2577,7 +2577,7 @@
         <v>4</v>
       </c>
       <c r="Y5" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z5" s="4">
         <v>3</v>
@@ -2782,7 +2782,7 @@
         <v>0</v>
       </c>
       <c r="AD7" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE7" s="4">
         <v>3</v>
@@ -2903,7 +2903,7 @@
         <v>3</v>
       </c>
       <c r="G9" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H9" s="4">
         <v>0</v>
@@ -2924,7 +2924,7 @@
         <v>3</v>
       </c>
       <c r="N9" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O9" s="4">
         <v>0</v>

--- a/target.xlsx
+++ b/target.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\백업폴더\딱따구리\AI\강북도매 영업관리 포털\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A1BBBF1-E804-4D1D-A66D-135D7038EA62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F2FAD15-1333-4F6B-AA80-33E3A2C9249D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F51F585E-D8DA-4EE1-A615-D4BBA305B88C}"/>
   </bookViews>
@@ -683,7 +683,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -703,6 +703,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1146,961 +1149,992 @@
   <sheetPr>
     <tabColor theme="1"/>
   </sheetPr>
-  <dimension ref="A1:AE10"/>
+  <dimension ref="A1:AF10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.58203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="31" width="5.25" style="1" customWidth="1"/>
-    <col min="32" max="16384" width="9" style="1"/>
+    <col min="32" max="32" width="6" style="1" customWidth="1"/>
+    <col min="33" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="6">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="C1" s="6">
-        <v>46175</v>
+        <v>46205</v>
       </c>
       <c r="D1" s="6">
-        <v>46176</v>
+        <v>46206</v>
       </c>
       <c r="E1" s="6">
-        <v>46177</v>
+        <v>46207</v>
       </c>
       <c r="F1" s="6">
-        <v>46178</v>
+        <v>46208</v>
       </c>
       <c r="G1" s="6">
-        <v>46179</v>
+        <v>46209</v>
       </c>
       <c r="H1" s="6">
-        <v>46180</v>
+        <v>46210</v>
       </c>
       <c r="I1" s="6">
-        <v>46181</v>
+        <v>46211</v>
       </c>
       <c r="J1" s="6">
-        <v>46182</v>
+        <v>46212</v>
       </c>
       <c r="K1" s="6">
-        <v>46183</v>
+        <v>46213</v>
       </c>
       <c r="L1" s="6">
-        <v>46184</v>
+        <v>46214</v>
       </c>
       <c r="M1" s="6">
-        <v>46185</v>
+        <v>46215</v>
       </c>
       <c r="N1" s="6">
-        <v>46186</v>
+        <v>46216</v>
       </c>
       <c r="O1" s="6">
-        <v>46187</v>
+        <v>46217</v>
       </c>
       <c r="P1" s="6">
-        <v>46188</v>
+        <v>46218</v>
       </c>
       <c r="Q1" s="6">
-        <v>46189</v>
+        <v>46219</v>
       </c>
       <c r="R1" s="6">
-        <v>46190</v>
+        <v>46220</v>
       </c>
       <c r="S1" s="6">
-        <v>46191</v>
+        <v>46221</v>
       </c>
       <c r="T1" s="6">
-        <v>46192</v>
+        <v>46222</v>
       </c>
       <c r="U1" s="6">
-        <v>46193</v>
+        <v>46223</v>
       </c>
       <c r="V1" s="6">
-        <v>46194</v>
+        <v>46224</v>
       </c>
       <c r="W1" s="6">
-        <v>46195</v>
+        <v>46225</v>
       </c>
       <c r="X1" s="6">
-        <v>46196</v>
+        <v>46226</v>
       </c>
       <c r="Y1" s="6">
-        <v>46197</v>
+        <v>46227</v>
       </c>
       <c r="Z1" s="6">
-        <v>46198</v>
+        <v>46228</v>
       </c>
       <c r="AA1" s="6">
-        <v>46199</v>
+        <v>46229</v>
       </c>
       <c r="AB1" s="6">
-        <v>46200</v>
+        <v>46230</v>
       </c>
       <c r="AC1" s="6">
-        <v>46201</v>
+        <v>46231</v>
       </c>
       <c r="AD1" s="6">
-        <v>46202</v>
+        <v>46232</v>
       </c>
       <c r="AE1" s="6">
-        <v>46203</v>
+        <v>46233</v>
+      </c>
+      <c r="AF1" s="6">
+        <v>46234</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="7">
+        <v>17</v>
+      </c>
+      <c r="C2" s="7">
+        <v>17</v>
+      </c>
+      <c r="D2" s="7">
+        <v>17</v>
+      </c>
+      <c r="E2" s="7">
+        <v>22</v>
+      </c>
+      <c r="F2" s="7">
+        <v>0</v>
+      </c>
+      <c r="G2" s="7">
+        <v>25</v>
+      </c>
+      <c r="H2" s="7">
+        <v>17</v>
+      </c>
+      <c r="I2" s="7">
+        <v>17</v>
+      </c>
+      <c r="J2" s="7">
+        <v>17</v>
+      </c>
+      <c r="K2" s="7">
+        <v>17</v>
+      </c>
+      <c r="L2" s="7">
+        <v>22</v>
+      </c>
+      <c r="M2" s="7">
+        <v>0</v>
+      </c>
+      <c r="N2" s="7">
+        <v>25</v>
+      </c>
+      <c r="O2" s="7">
+        <v>17</v>
+      </c>
+      <c r="P2" s="7">
+        <v>17</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>17</v>
+      </c>
+      <c r="R2" s="7">
+        <v>17</v>
+      </c>
+      <c r="S2" s="7">
+        <v>22</v>
+      </c>
+      <c r="T2" s="7">
+        <v>0</v>
+      </c>
+      <c r="U2" s="7">
+        <v>25</v>
+      </c>
+      <c r="V2" s="7">
+        <v>17</v>
+      </c>
+      <c r="W2" s="7">
+        <v>17</v>
+      </c>
+      <c r="X2" s="7">
+        <v>18</v>
+      </c>
+      <c r="Y2" s="7">
+        <v>18</v>
+      </c>
+      <c r="Z2" s="7">
+        <v>23</v>
+      </c>
+      <c r="AA2" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="7">
         <v>26</v>
       </c>
-      <c r="C2" s="4">
-        <v>17</v>
-      </c>
-      <c r="D2" s="4">
-        <v>17</v>
-      </c>
-      <c r="E2" s="4">
-        <v>17</v>
-      </c>
-      <c r="F2" s="4">
-        <v>17</v>
-      </c>
-      <c r="G2" s="4">
-        <v>22</v>
-      </c>
-      <c r="H2" s="4">
-        <v>0</v>
-      </c>
-      <c r="I2" s="4">
-        <v>26</v>
-      </c>
-      <c r="J2" s="4">
-        <v>17</v>
-      </c>
-      <c r="K2" s="4">
-        <v>17</v>
-      </c>
-      <c r="L2" s="4">
-        <v>17</v>
-      </c>
-      <c r="M2" s="4">
-        <v>17</v>
-      </c>
-      <c r="N2" s="4">
-        <v>22</v>
-      </c>
-      <c r="O2" s="4">
-        <v>0</v>
-      </c>
-      <c r="P2" s="4">
-        <v>27</v>
-      </c>
-      <c r="Q2" s="4">
+      <c r="AC2" s="7">
         <v>18</v>
       </c>
-      <c r="R2" s="4">
+      <c r="AD2" s="7">
         <v>18</v>
       </c>
-      <c r="S2" s="4">
+      <c r="AE2" s="7">
         <v>18</v>
       </c>
-      <c r="T2" s="4">
+      <c r="AF2" s="7">
         <v>18</v>
       </c>
-      <c r="U2" s="4">
-        <v>23</v>
-      </c>
-      <c r="V2" s="4">
-        <v>0</v>
-      </c>
-      <c r="W2" s="4">
-        <v>26</v>
-      </c>
-      <c r="X2" s="4">
-        <v>18</v>
-      </c>
-      <c r="Y2" s="4">
-        <v>18</v>
-      </c>
-      <c r="Z2" s="4">
-        <v>18</v>
-      </c>
-      <c r="AA2" s="4">
-        <v>18</v>
-      </c>
-      <c r="AB2" s="4">
-        <v>23</v>
-      </c>
-      <c r="AC2" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="4">
-        <v>26</v>
-      </c>
-      <c r="AE2" s="4">
-        <v>18</v>
-      </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="7">
+        <v>13</v>
+      </c>
+      <c r="C3" s="7">
+        <v>13</v>
+      </c>
+      <c r="D3" s="7">
+        <v>13</v>
+      </c>
+      <c r="E3" s="7">
+        <v>18</v>
+      </c>
+      <c r="F3" s="7">
+        <v>0</v>
+      </c>
+      <c r="G3" s="7">
         <v>21</v>
       </c>
-      <c r="C3" s="4">
+      <c r="H3" s="7">
+        <v>13</v>
+      </c>
+      <c r="I3" s="7">
+        <v>13</v>
+      </c>
+      <c r="J3" s="7">
+        <v>13</v>
+      </c>
+      <c r="K3" s="7">
+        <v>13</v>
+      </c>
+      <c r="L3" s="7">
+        <v>19</v>
+      </c>
+      <c r="M3" s="7">
+        <v>0</v>
+      </c>
+      <c r="N3" s="7">
+        <v>22</v>
+      </c>
+      <c r="O3" s="7">
         <v>14</v>
       </c>
-      <c r="D3" s="4">
+      <c r="P3" s="7">
         <v>14</v>
       </c>
-      <c r="E3" s="4">
+      <c r="Q3" s="7">
         <v>14</v>
       </c>
-      <c r="F3" s="4">
+      <c r="R3" s="7">
         <v>14</v>
       </c>
-      <c r="G3" s="4">
-        <v>18</v>
-      </c>
-      <c r="H3" s="4">
-        <v>0</v>
-      </c>
-      <c r="I3" s="4">
-        <v>21</v>
-      </c>
-      <c r="J3" s="4">
+      <c r="S3" s="7">
+        <v>19</v>
+      </c>
+      <c r="T3" s="7">
+        <v>0</v>
+      </c>
+      <c r="U3" s="7">
+        <v>22</v>
+      </c>
+      <c r="V3" s="7">
         <v>14</v>
       </c>
-      <c r="K3" s="4">
+      <c r="W3" s="7">
         <v>14</v>
       </c>
-      <c r="L3" s="4">
+      <c r="X3" s="7">
         <v>14</v>
       </c>
-      <c r="M3" s="4">
+      <c r="Y3" s="7">
         <v>14</v>
       </c>
-      <c r="N3" s="4">
-        <v>18</v>
-      </c>
-      <c r="O3" s="4">
-        <v>0</v>
-      </c>
-      <c r="P3" s="4">
-        <v>21</v>
-      </c>
-      <c r="Q3" s="4">
+      <c r="Z3" s="7">
+        <v>19</v>
+      </c>
+      <c r="AA3" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="7">
+        <v>22</v>
+      </c>
+      <c r="AC3" s="7">
         <v>14</v>
       </c>
-      <c r="R3" s="4">
+      <c r="AD3" s="7">
+        <v>14</v>
+      </c>
+      <c r="AE3" s="7">
+        <v>14</v>
+      </c>
+      <c r="AF3" s="7">
         <v>15</v>
       </c>
-      <c r="S3" s="4">
-        <v>15</v>
-      </c>
-      <c r="T3" s="4">
-        <v>15</v>
-      </c>
-      <c r="U3" s="4">
-        <v>19</v>
-      </c>
-      <c r="V3" s="4">
-        <v>0</v>
-      </c>
-      <c r="W3" s="4">
-        <v>22</v>
-      </c>
-      <c r="X3" s="4">
-        <v>14</v>
-      </c>
-      <c r="Y3" s="4">
-        <v>14</v>
-      </c>
-      <c r="Z3" s="4">
-        <v>14</v>
-      </c>
-      <c r="AA3" s="4">
-        <v>14</v>
-      </c>
-      <c r="AB3" s="4">
-        <v>19</v>
-      </c>
-      <c r="AC3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="4">
-        <v>22</v>
-      </c>
-      <c r="AE3" s="4">
-        <v>14</v>
-      </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="7">
+        <v>19</v>
+      </c>
+      <c r="C4" s="7">
+        <v>19</v>
+      </c>
+      <c r="D4" s="7">
+        <v>19</v>
+      </c>
+      <c r="E4" s="7">
+        <v>24</v>
+      </c>
+      <c r="F4" s="7">
+        <v>0</v>
+      </c>
+      <c r="G4" s="7">
+        <v>28</v>
+      </c>
+      <c r="H4" s="7">
+        <v>19</v>
+      </c>
+      <c r="I4" s="7">
+        <v>19</v>
+      </c>
+      <c r="J4" s="7">
+        <v>19</v>
+      </c>
+      <c r="K4" s="7">
+        <v>19</v>
+      </c>
+      <c r="L4" s="7">
+        <v>24</v>
+      </c>
+      <c r="M4" s="7">
+        <v>0</v>
+      </c>
+      <c r="N4" s="7">
+        <v>28</v>
+      </c>
+      <c r="O4" s="7">
+        <v>19</v>
+      </c>
+      <c r="P4" s="7">
+        <v>19</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>19</v>
+      </c>
+      <c r="R4" s="7">
+        <v>19</v>
+      </c>
+      <c r="S4" s="7">
+        <v>24</v>
+      </c>
+      <c r="T4" s="7">
+        <v>0</v>
+      </c>
+      <c r="U4" s="7">
+        <v>28</v>
+      </c>
+      <c r="V4" s="7">
+        <v>20</v>
+      </c>
+      <c r="W4" s="7">
+        <v>20</v>
+      </c>
+      <c r="X4" s="7">
+        <v>20</v>
+      </c>
+      <c r="Y4" s="7">
+        <v>20</v>
+      </c>
+      <c r="Z4" s="7">
+        <v>25</v>
+      </c>
+      <c r="AA4" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="7">
         <v>29</v>
       </c>
-      <c r="C4" s="4">
+      <c r="AC4" s="7">
+        <v>20</v>
+      </c>
+      <c r="AD4" s="7">
+        <v>20</v>
+      </c>
+      <c r="AE4" s="7">
+        <v>20</v>
+      </c>
+      <c r="AF4" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7">
         <v>19</v>
       </c>
-      <c r="D4" s="4">
+      <c r="C5" s="7">
         <v>19</v>
       </c>
-      <c r="E4" s="4">
+      <c r="D5" s="7">
         <v>19</v>
       </c>
-      <c r="F4" s="4">
+      <c r="E5" s="7">
+        <v>25</v>
+      </c>
+      <c r="F5" s="7">
+        <v>0</v>
+      </c>
+      <c r="G5" s="7">
+        <v>29</v>
+      </c>
+      <c r="H5" s="7">
         <v>19</v>
       </c>
-      <c r="G4" s="4">
+      <c r="I5" s="7">
+        <v>19</v>
+      </c>
+      <c r="J5" s="7">
+        <v>19</v>
+      </c>
+      <c r="K5" s="7">
+        <v>19</v>
+      </c>
+      <c r="L5" s="7">
         <v>25</v>
       </c>
-      <c r="H4" s="4">
-        <v>0</v>
-      </c>
-      <c r="I4" s="4">
+      <c r="M5" s="7">
+        <v>0</v>
+      </c>
+      <c r="N5" s="7">
         <v>29</v>
       </c>
-      <c r="J4" s="4">
+      <c r="O5" s="7">
         <v>19</v>
       </c>
-      <c r="K4" s="4">
+      <c r="P5" s="7">
         <v>19</v>
       </c>
-      <c r="L4" s="4">
+      <c r="Q5" s="7">
         <v>19</v>
       </c>
-      <c r="M4" s="4">
+      <c r="R5" s="7">
         <v>19</v>
       </c>
-      <c r="N4" s="4">
+      <c r="S5" s="7">
+        <v>25</v>
+      </c>
+      <c r="T5" s="7">
+        <v>0</v>
+      </c>
+      <c r="U5" s="7">
+        <v>30</v>
+      </c>
+      <c r="V5" s="7">
+        <v>20</v>
+      </c>
+      <c r="W5" s="7">
+        <v>20</v>
+      </c>
+      <c r="X5" s="7">
+        <v>20</v>
+      </c>
+      <c r="Y5" s="7">
+        <v>20</v>
+      </c>
+      <c r="Z5" s="7">
         <v>26</v>
       </c>
-      <c r="O4" s="4">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4">
+      <c r="AA5" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="7">
         <v>30</v>
       </c>
-      <c r="Q4" s="4">
+      <c r="AC5" s="7">
         <v>20</v>
       </c>
-      <c r="R4" s="4">
+      <c r="AD5" s="7">
         <v>20</v>
       </c>
-      <c r="S4" s="4">
+      <c r="AE5" s="7">
         <v>20</v>
       </c>
-      <c r="T4" s="4">
+      <c r="AF5" s="7">
         <v>20</v>
       </c>
-      <c r="U4" s="4">
-        <v>25</v>
-      </c>
-      <c r="V4" s="4">
-        <v>0</v>
-      </c>
-      <c r="W4" s="4">
-        <v>29</v>
-      </c>
-      <c r="X4" s="4">
-        <v>20</v>
-      </c>
-      <c r="Y4" s="4">
-        <v>20</v>
-      </c>
-      <c r="Z4" s="4">
-        <v>20</v>
-      </c>
-      <c r="AA4" s="4">
-        <v>20</v>
-      </c>
-      <c r="AB4" s="4">
-        <v>25</v>
-      </c>
-      <c r="AC4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="4">
-        <v>29</v>
-      </c>
-      <c r="AE4" s="4">
-        <v>20</v>
-      </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4">
-        <v>29</v>
-      </c>
-      <c r="C5" s="4">
-        <v>19</v>
-      </c>
-      <c r="D5" s="4">
-        <v>19</v>
-      </c>
-      <c r="E5" s="4">
-        <v>19</v>
-      </c>
-      <c r="F5" s="4">
-        <v>19</v>
-      </c>
-      <c r="G5" s="4">
-        <v>25</v>
-      </c>
-      <c r="H5" s="4">
-        <v>0</v>
-      </c>
-      <c r="I5" s="4">
-        <v>30</v>
-      </c>
-      <c r="J5" s="4">
-        <v>20</v>
-      </c>
-      <c r="K5" s="4">
-        <v>20</v>
-      </c>
-      <c r="L5" s="4">
-        <v>20</v>
-      </c>
-      <c r="M5" s="4">
-        <v>20</v>
-      </c>
-      <c r="N5" s="4">
-        <v>26</v>
-      </c>
-      <c r="O5" s="4">
-        <v>0</v>
-      </c>
-      <c r="P5" s="4">
-        <v>30</v>
-      </c>
-      <c r="Q5" s="4">
-        <v>20</v>
-      </c>
-      <c r="R5" s="4">
-        <v>20</v>
-      </c>
-      <c r="S5" s="4">
-        <v>20</v>
-      </c>
-      <c r="T5" s="4">
-        <v>20</v>
-      </c>
-      <c r="U5" s="4">
-        <v>26</v>
-      </c>
-      <c r="V5" s="4">
-        <v>0</v>
-      </c>
-      <c r="W5" s="4">
-        <v>30</v>
-      </c>
-      <c r="X5" s="4">
-        <v>20</v>
-      </c>
-      <c r="Y5" s="4">
-        <v>20</v>
-      </c>
-      <c r="Z5" s="4">
-        <v>20</v>
-      </c>
-      <c r="AA5" s="4">
-        <v>20</v>
-      </c>
-      <c r="AB5" s="4">
-        <v>26</v>
-      </c>
-      <c r="AC5" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="4">
-        <v>30</v>
-      </c>
-      <c r="AE5" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="7">
+        <v>23</v>
+      </c>
+      <c r="C6" s="7">
+        <v>23</v>
+      </c>
+      <c r="D6" s="7">
+        <v>23</v>
+      </c>
+      <c r="E6" s="7">
+        <v>31</v>
+      </c>
+      <c r="F6" s="7">
+        <v>0</v>
+      </c>
+      <c r="G6" s="7">
         <v>36</v>
       </c>
-      <c r="C6" s="4">
+      <c r="H6" s="7">
+        <v>23</v>
+      </c>
+      <c r="I6" s="7">
+        <v>23</v>
+      </c>
+      <c r="J6" s="7">
+        <v>23</v>
+      </c>
+      <c r="K6" s="7">
+        <v>23</v>
+      </c>
+      <c r="L6" s="7">
+        <v>31</v>
+      </c>
+      <c r="M6" s="7">
+        <v>0</v>
+      </c>
+      <c r="N6" s="7">
+        <v>36</v>
+      </c>
+      <c r="O6" s="7">
+        <v>23</v>
+      </c>
+      <c r="P6" s="7">
         <v>24</v>
       </c>
-      <c r="D6" s="4">
+      <c r="Q6" s="7">
         <v>24</v>
       </c>
-      <c r="E6" s="4">
+      <c r="R6" s="7">
         <v>24</v>
       </c>
-      <c r="F6" s="4">
+      <c r="S6" s="7">
+        <v>32</v>
+      </c>
+      <c r="T6" s="7">
+        <v>0</v>
+      </c>
+      <c r="U6" s="7">
+        <v>37</v>
+      </c>
+      <c r="V6" s="7">
         <v>24</v>
       </c>
-      <c r="G6" s="4">
-        <v>31</v>
-      </c>
-      <c r="H6" s="4">
-        <v>0</v>
-      </c>
-      <c r="I6" s="4">
-        <v>36</v>
-      </c>
-      <c r="J6" s="4">
+      <c r="W6" s="7">
         <v>24</v>
       </c>
-      <c r="K6" s="4">
+      <c r="X6" s="7">
         <v>24</v>
       </c>
-      <c r="L6" s="4">
+      <c r="Y6" s="7">
         <v>24</v>
       </c>
-      <c r="M6" s="4">
+      <c r="Z6" s="7">
+        <v>32</v>
+      </c>
+      <c r="AA6" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="7">
+        <v>37</v>
+      </c>
+      <c r="AC6" s="7">
         <v>24</v>
       </c>
-      <c r="N6" s="4">
-        <v>31</v>
-      </c>
-      <c r="O6" s="4">
-        <v>0</v>
-      </c>
-      <c r="P6" s="4">
-        <v>37</v>
-      </c>
-      <c r="Q6" s="4">
+      <c r="AD6" s="7">
+        <v>24</v>
+      </c>
+      <c r="AE6" s="7">
+        <v>24</v>
+      </c>
+      <c r="AF6" s="7">
         <v>25</v>
       </c>
-      <c r="R6" s="4">
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7">
+        <v>16</v>
+      </c>
+      <c r="C7" s="7">
+        <v>16</v>
+      </c>
+      <c r="D7" s="7">
+        <v>16</v>
+      </c>
+      <c r="E7" s="7">
+        <v>21</v>
+      </c>
+      <c r="F7" s="7">
+        <v>0</v>
+      </c>
+      <c r="G7" s="7">
+        <v>24</v>
+      </c>
+      <c r="H7" s="7">
+        <v>16</v>
+      </c>
+      <c r="I7" s="7">
+        <v>16</v>
+      </c>
+      <c r="J7" s="7">
+        <v>16</v>
+      </c>
+      <c r="K7" s="7">
+        <v>16</v>
+      </c>
+      <c r="L7" s="7">
+        <v>21</v>
+      </c>
+      <c r="M7" s="7">
+        <v>0</v>
+      </c>
+      <c r="N7" s="7">
+        <v>24</v>
+      </c>
+      <c r="O7" s="7">
+        <v>16</v>
+      </c>
+      <c r="P7" s="7">
+        <v>16</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>17</v>
+      </c>
+      <c r="R7" s="7">
+        <v>17</v>
+      </c>
+      <c r="S7" s="7">
+        <v>22</v>
+      </c>
+      <c r="T7" s="7">
+        <v>0</v>
+      </c>
+      <c r="U7" s="7">
         <v>25</v>
       </c>
-      <c r="S6" s="4">
+      <c r="V7" s="7">
+        <v>17</v>
+      </c>
+      <c r="W7" s="7">
+        <v>17</v>
+      </c>
+      <c r="X7" s="7">
+        <v>17</v>
+      </c>
+      <c r="Y7" s="7">
+        <v>17</v>
+      </c>
+      <c r="Z7" s="7">
+        <v>22</v>
+      </c>
+      <c r="AA7" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="7">
         <v>25</v>
       </c>
-      <c r="T6" s="4">
-        <v>25</v>
-      </c>
-      <c r="U6" s="4">
-        <v>32</v>
-      </c>
-      <c r="V6" s="4">
-        <v>0</v>
-      </c>
-      <c r="W6" s="4">
-        <v>37</v>
-      </c>
-      <c r="X6" s="4">
-        <v>24</v>
-      </c>
-      <c r="Y6" s="4">
-        <v>24</v>
-      </c>
-      <c r="Z6" s="4">
-        <v>24</v>
-      </c>
-      <c r="AA6" s="4">
-        <v>24</v>
-      </c>
-      <c r="AB6" s="4">
-        <v>32</v>
-      </c>
-      <c r="AC6" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="4">
-        <v>37</v>
-      </c>
-      <c r="AE6" s="4">
-        <v>24</v>
+      <c r="AC7" s="7">
+        <v>17</v>
+      </c>
+      <c r="AD7" s="7">
+        <v>17</v>
+      </c>
+      <c r="AE7" s="7">
+        <v>17</v>
+      </c>
+      <c r="AF7" s="7">
+        <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A7" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4">
-        <v>25</v>
-      </c>
-      <c r="C7" s="4">
-        <v>16</v>
-      </c>
-      <c r="D7" s="4">
-        <v>16</v>
-      </c>
-      <c r="E7" s="4">
-        <v>16</v>
-      </c>
-      <c r="F7" s="4">
-        <v>16</v>
-      </c>
-      <c r="G7" s="4">
-        <v>21</v>
-      </c>
-      <c r="H7" s="4">
-        <v>0</v>
-      </c>
-      <c r="I7" s="4">
-        <v>25</v>
-      </c>
-      <c r="J7" s="4">
-        <v>17</v>
-      </c>
-      <c r="K7" s="4">
-        <v>17</v>
-      </c>
-      <c r="L7" s="4">
-        <v>17</v>
-      </c>
-      <c r="M7" s="4">
-        <v>17</v>
-      </c>
-      <c r="N7" s="4">
-        <v>22</v>
-      </c>
-      <c r="O7" s="4">
-        <v>0</v>
-      </c>
-      <c r="P7" s="4">
-        <v>26</v>
-      </c>
-      <c r="Q7" s="4">
-        <v>17</v>
-      </c>
-      <c r="R7" s="4">
-        <v>17</v>
-      </c>
-      <c r="S7" s="4">
-        <v>17</v>
-      </c>
-      <c r="T7" s="4">
-        <v>17</v>
-      </c>
-      <c r="U7" s="4">
-        <v>22</v>
-      </c>
-      <c r="V7" s="4">
-        <v>0</v>
-      </c>
-      <c r="W7" s="4">
-        <v>25</v>
-      </c>
-      <c r="X7" s="4">
-        <v>17</v>
-      </c>
-      <c r="Y7" s="4">
-        <v>17</v>
-      </c>
-      <c r="Z7" s="4">
-        <v>17</v>
-      </c>
-      <c r="AA7" s="4">
-        <v>17</v>
-      </c>
-      <c r="AB7" s="4">
-        <v>22</v>
-      </c>
-      <c r="AC7" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="4">
-        <v>25</v>
-      </c>
-      <c r="AE7" s="4">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="7">
+        <v>14</v>
+      </c>
+      <c r="C8" s="7">
+        <v>14</v>
+      </c>
+      <c r="D8" s="7">
+        <v>14</v>
+      </c>
+      <c r="E8" s="7">
+        <v>18</v>
+      </c>
+      <c r="F8" s="7">
+        <v>0</v>
+      </c>
+      <c r="G8" s="7">
+        <v>21</v>
+      </c>
+      <c r="H8" s="7">
+        <v>14</v>
+      </c>
+      <c r="I8" s="7">
+        <v>14</v>
+      </c>
+      <c r="J8" s="7">
+        <v>14</v>
+      </c>
+      <c r="K8" s="7">
+        <v>14</v>
+      </c>
+      <c r="L8" s="7">
+        <v>18</v>
+      </c>
+      <c r="M8" s="7">
+        <v>0</v>
+      </c>
+      <c r="N8" s="7">
+        <v>21</v>
+      </c>
+      <c r="O8" s="7">
+        <v>14</v>
+      </c>
+      <c r="P8" s="7">
+        <v>15</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>15</v>
+      </c>
+      <c r="R8" s="7">
+        <v>15</v>
+      </c>
+      <c r="S8" s="7">
+        <v>19</v>
+      </c>
+      <c r="T8" s="7">
+        <v>0</v>
+      </c>
+      <c r="U8" s="7">
         <v>22</v>
       </c>
-      <c r="C8" s="4">
-        <v>14</v>
-      </c>
-      <c r="D8" s="4">
-        <v>14</v>
-      </c>
-      <c r="E8" s="4">
-        <v>14</v>
-      </c>
-      <c r="F8" s="4">
-        <v>14</v>
-      </c>
-      <c r="G8" s="4">
+      <c r="V8" s="7">
+        <v>15</v>
+      </c>
+      <c r="W8" s="7">
+        <v>15</v>
+      </c>
+      <c r="X8" s="7">
+        <v>15</v>
+      </c>
+      <c r="Y8" s="7">
+        <v>15</v>
+      </c>
+      <c r="Z8" s="7">
         <v>19</v>
       </c>
-      <c r="H8" s="4">
-        <v>0</v>
-      </c>
-      <c r="I8" s="4">
+      <c r="AA8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="7">
         <v>22</v>
       </c>
-      <c r="J8" s="4">
-        <v>14</v>
-      </c>
-      <c r="K8" s="4">
-        <v>14</v>
-      </c>
-      <c r="L8" s="4">
+      <c r="AC8" s="7">
         <v>15</v>
       </c>
-      <c r="M8" s="4">
+      <c r="AD8" s="7">
         <v>15</v>
       </c>
-      <c r="N8" s="4">
-        <v>20</v>
-      </c>
-      <c r="O8" s="4">
-        <v>0</v>
-      </c>
-      <c r="P8" s="4">
-        <v>23</v>
-      </c>
-      <c r="Q8" s="4">
+      <c r="AE8" s="7">
         <v>15</v>
       </c>
-      <c r="R8" s="4">
+      <c r="AF8" s="7">
         <v>15</v>
       </c>
-      <c r="S8" s="4">
-        <v>15</v>
-      </c>
-      <c r="T8" s="4">
-        <v>15</v>
-      </c>
-      <c r="U8" s="4">
-        <v>19</v>
-      </c>
-      <c r="V8" s="4">
-        <v>0</v>
-      </c>
-      <c r="W8" s="4">
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="7">
+        <v>16</v>
+      </c>
+      <c r="C9" s="7">
+        <v>16</v>
+      </c>
+      <c r="D9" s="7">
+        <v>16</v>
+      </c>
+      <c r="E9" s="7">
+        <v>21</v>
+      </c>
+      <c r="F9" s="7">
+        <v>0</v>
+      </c>
+      <c r="G9" s="7">
+        <v>24</v>
+      </c>
+      <c r="H9" s="7">
+        <v>16</v>
+      </c>
+      <c r="I9" s="7">
+        <v>16</v>
+      </c>
+      <c r="J9" s="7">
+        <v>16</v>
+      </c>
+      <c r="K9" s="7">
+        <v>16</v>
+      </c>
+      <c r="L9" s="7">
+        <v>21</v>
+      </c>
+      <c r="M9" s="7">
+        <v>0</v>
+      </c>
+      <c r="N9" s="7">
+        <v>24</v>
+      </c>
+      <c r="O9" s="7">
+        <v>16</v>
+      </c>
+      <c r="P9" s="7">
+        <v>16</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>16</v>
+      </c>
+      <c r="R9" s="7">
+        <v>16</v>
+      </c>
+      <c r="S9" s="7">
+        <v>21</v>
+      </c>
+      <c r="T9" s="7">
+        <v>0</v>
+      </c>
+      <c r="U9" s="7">
+        <v>24</v>
+      </c>
+      <c r="V9" s="7">
+        <v>17</v>
+      </c>
+      <c r="W9" s="7">
+        <v>17</v>
+      </c>
+      <c r="X9" s="7">
+        <v>17</v>
+      </c>
+      <c r="Y9" s="7">
+        <v>17</v>
+      </c>
+      <c r="Z9" s="7">
         <v>22</v>
       </c>
-      <c r="X8" s="4">
-        <v>15</v>
-      </c>
-      <c r="Y8" s="4">
-        <v>15</v>
-      </c>
-      <c r="Z8" s="4">
-        <v>15</v>
-      </c>
-      <c r="AA8" s="4">
-        <v>15</v>
-      </c>
-      <c r="AB8" s="4">
-        <v>19</v>
-      </c>
-      <c r="AC8" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="4">
-        <v>22</v>
-      </c>
-      <c r="AE8" s="4">
-        <v>15</v>
+      <c r="AA9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="7">
+        <v>25</v>
+      </c>
+      <c r="AC9" s="7">
+        <v>17</v>
+      </c>
+      <c r="AD9" s="7">
+        <v>17</v>
+      </c>
+      <c r="AE9" s="7">
+        <v>17</v>
+      </c>
+      <c r="AF9" s="7">
+        <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="4">
-        <v>25</v>
-      </c>
-      <c r="C9" s="4">
-        <v>16</v>
-      </c>
-      <c r="D9" s="4">
-        <v>16</v>
-      </c>
-      <c r="E9" s="4">
-        <v>16</v>
-      </c>
-      <c r="F9" s="4">
-        <v>16</v>
-      </c>
-      <c r="G9" s="4">
-        <v>21</v>
-      </c>
-      <c r="H9" s="4">
-        <v>0</v>
-      </c>
-      <c r="I9" s="4">
-        <v>25</v>
-      </c>
-      <c r="J9" s="4">
-        <v>16</v>
-      </c>
-      <c r="K9" s="4">
-        <v>16</v>
-      </c>
-      <c r="L9" s="4">
-        <v>16</v>
-      </c>
-      <c r="M9" s="4">
-        <v>16</v>
-      </c>
-      <c r="N9" s="4">
-        <v>22</v>
-      </c>
-      <c r="O9" s="4">
-        <v>0</v>
-      </c>
-      <c r="P9" s="4">
-        <v>26</v>
-      </c>
-      <c r="Q9" s="4">
-        <v>17</v>
-      </c>
-      <c r="R9" s="4">
-        <v>17</v>
-      </c>
-      <c r="S9" s="4">
-        <v>17</v>
-      </c>
-      <c r="T9" s="4">
-        <v>17</v>
-      </c>
-      <c r="U9" s="4">
-        <v>22</v>
-      </c>
-      <c r="V9" s="4">
-        <v>0</v>
-      </c>
-      <c r="W9" s="4">
-        <v>25</v>
-      </c>
-      <c r="X9" s="4">
-        <v>17</v>
-      </c>
-      <c r="Y9" s="4">
-        <v>17</v>
-      </c>
-      <c r="Z9" s="4">
-        <v>17</v>
-      </c>
-      <c r="AA9" s="4">
-        <v>17</v>
-      </c>
-      <c r="AB9" s="4">
-        <v>22</v>
-      </c>
-      <c r="AC9" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="4">
-        <v>25</v>
-      </c>
-      <c r="AE9" s="4">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="7">
+        <v>15</v>
+      </c>
+      <c r="C10" s="7">
+        <v>15</v>
+      </c>
+      <c r="D10" s="7">
+        <v>15</v>
+      </c>
+      <c r="E10" s="7">
+        <v>19</v>
+      </c>
+      <c r="F10" s="7">
+        <v>0</v>
+      </c>
+      <c r="G10" s="7">
         <v>23</v>
       </c>
-      <c r="C10" s="4">
+      <c r="H10" s="7">
         <v>15</v>
       </c>
-      <c r="D10" s="4">
+      <c r="I10" s="7">
         <v>15</v>
       </c>
-      <c r="E10" s="4">
+      <c r="J10" s="7">
         <v>15</v>
       </c>
-      <c r="F10" s="4">
+      <c r="K10" s="7">
         <v>15</v>
       </c>
-      <c r="G10" s="4">
+      <c r="L10" s="7">
+        <v>19</v>
+      </c>
+      <c r="M10" s="7">
+        <v>0</v>
+      </c>
+      <c r="N10" s="7">
+        <v>23</v>
+      </c>
+      <c r="O10" s="7">
+        <v>15</v>
+      </c>
+      <c r="P10" s="7">
+        <v>15</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>15</v>
+      </c>
+      <c r="R10" s="7">
+        <v>15</v>
+      </c>
+      <c r="S10" s="7">
+        <v>19</v>
+      </c>
+      <c r="T10" s="7">
+        <v>0</v>
+      </c>
+      <c r="U10" s="7">
+        <v>23</v>
+      </c>
+      <c r="V10" s="7">
+        <v>16</v>
+      </c>
+      <c r="W10" s="7">
+        <v>16</v>
+      </c>
+      <c r="X10" s="7">
+        <v>16</v>
+      </c>
+      <c r="Y10" s="7">
+        <v>16</v>
+      </c>
+      <c r="Z10" s="7">
         <v>20</v>
       </c>
-      <c r="H10" s="4">
-        <v>0</v>
-      </c>
-      <c r="I10" s="4">
-        <v>23</v>
-      </c>
-      <c r="J10" s="4">
-        <v>15</v>
-      </c>
-      <c r="K10" s="4">
-        <v>15</v>
-      </c>
-      <c r="L10" s="4">
-        <v>15</v>
-      </c>
-      <c r="M10" s="4">
-        <v>15</v>
-      </c>
-      <c r="N10" s="4">
-        <v>21</v>
-      </c>
-      <c r="O10" s="4">
-        <v>0</v>
-      </c>
-      <c r="P10" s="4">
+      <c r="AA10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="7">
         <v>24</v>
       </c>
-      <c r="Q10" s="4">
+      <c r="AC10" s="7">
         <v>16</v>
       </c>
-      <c r="R10" s="4">
+      <c r="AD10" s="7">
         <v>16</v>
       </c>
-      <c r="S10" s="4">
+      <c r="AE10" s="7">
         <v>16</v>
       </c>
-      <c r="T10" s="4">
-        <v>16</v>
-      </c>
-      <c r="U10" s="4">
-        <v>20</v>
-      </c>
-      <c r="V10" s="4">
-        <v>0</v>
-      </c>
-      <c r="W10" s="4">
-        <v>24</v>
-      </c>
-      <c r="X10" s="4">
-        <v>16</v>
-      </c>
-      <c r="Y10" s="4">
-        <v>16</v>
-      </c>
-      <c r="Z10" s="4">
-        <v>16</v>
-      </c>
-      <c r="AA10" s="4">
-        <v>16</v>
-      </c>
-      <c r="AB10" s="4">
-        <v>20</v>
-      </c>
-      <c r="AC10" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="4">
-        <v>24</v>
-      </c>
-      <c r="AE10" s="4">
+      <c r="AF10" s="7">
         <v>16</v>
       </c>
     </row>
@@ -2116,589 +2150,607 @@
   <sheetPr>
     <tabColor theme="1"/>
   </sheetPr>
-  <dimension ref="A1:AE10"/>
+  <dimension ref="A1:AF10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="31" width="5.75" style="1" customWidth="1"/>
-    <col min="32" max="16384" width="9" style="1"/>
+    <col min="1" max="32" width="5.75" style="1" customWidth="1"/>
+    <col min="33" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="2">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="C1" s="2">
-        <v>46175</v>
+        <v>46205</v>
       </c>
       <c r="D1" s="2">
-        <v>46176</v>
+        <v>46206</v>
       </c>
       <c r="E1" s="2">
-        <v>46177</v>
+        <v>46207</v>
       </c>
       <c r="F1" s="2">
-        <v>46178</v>
+        <v>46208</v>
       </c>
       <c r="G1" s="2">
-        <v>46179</v>
+        <v>46209</v>
       </c>
       <c r="H1" s="2">
-        <v>46180</v>
+        <v>46210</v>
       </c>
       <c r="I1" s="2">
-        <v>46181</v>
+        <v>46211</v>
       </c>
       <c r="J1" s="2">
-        <v>46182</v>
+        <v>46212</v>
       </c>
       <c r="K1" s="2">
-        <v>46183</v>
+        <v>46213</v>
       </c>
       <c r="L1" s="2">
-        <v>46184</v>
+        <v>46214</v>
       </c>
       <c r="M1" s="2">
-        <v>46185</v>
+        <v>46215</v>
       </c>
       <c r="N1" s="2">
-        <v>46186</v>
+        <v>46216</v>
       </c>
       <c r="O1" s="2">
-        <v>46187</v>
+        <v>46217</v>
       </c>
       <c r="P1" s="2">
-        <v>46188</v>
+        <v>46218</v>
       </c>
       <c r="Q1" s="2">
-        <v>46189</v>
+        <v>46219</v>
       </c>
       <c r="R1" s="2">
-        <v>46190</v>
+        <v>46220</v>
       </c>
       <c r="S1" s="2">
-        <v>46191</v>
+        <v>46221</v>
       </c>
       <c r="T1" s="2">
-        <v>46192</v>
+        <v>46222</v>
       </c>
       <c r="U1" s="2">
-        <v>46193</v>
+        <v>46223</v>
       </c>
       <c r="V1" s="2">
-        <v>46194</v>
+        <v>46224</v>
       </c>
       <c r="W1" s="2">
-        <v>46195</v>
+        <v>46225</v>
       </c>
       <c r="X1" s="2">
-        <v>46196</v>
+        <v>46226</v>
       </c>
       <c r="Y1" s="2">
-        <v>46197</v>
+        <v>46227</v>
       </c>
       <c r="Z1" s="2">
-        <v>46198</v>
+        <v>46228</v>
       </c>
       <c r="AA1" s="2">
-        <v>46199</v>
+        <v>46229</v>
       </c>
       <c r="AB1" s="2">
-        <v>46200</v>
+        <v>46230</v>
       </c>
       <c r="AC1" s="2">
-        <v>46201</v>
+        <v>46231</v>
       </c>
       <c r="AD1" s="2">
-        <v>46202</v>
+        <v>46232</v>
       </c>
       <c r="AE1" s="2">
-        <v>46203</v>
+        <v>46233</v>
+      </c>
+      <c r="AF1" s="2">
+        <v>46234</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4">
+        <v>4</v>
+      </c>
+      <c r="C2" s="4">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
         <v>6</v>
       </c>
-      <c r="C2" s="4">
-        <v>4</v>
-      </c>
-      <c r="D2" s="4">
-        <v>4</v>
-      </c>
-      <c r="E2" s="4">
-        <v>4</v>
-      </c>
-      <c r="F2" s="4">
-        <v>4</v>
-      </c>
-      <c r="G2" s="4">
-        <v>5</v>
-      </c>
       <c r="H2" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I2" s="4">
+        <v>4</v>
+      </c>
+      <c r="J2" s="4">
+        <v>4</v>
+      </c>
+      <c r="K2" s="4">
+        <v>4</v>
+      </c>
+      <c r="L2" s="4">
+        <v>5</v>
+      </c>
+      <c r="M2" s="4">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4">
         <v>6</v>
       </c>
-      <c r="J2" s="4">
-        <v>4</v>
-      </c>
-      <c r="K2" s="4">
-        <v>4</v>
-      </c>
-      <c r="L2" s="4">
-        <v>4</v>
-      </c>
-      <c r="M2" s="4">
-        <v>4</v>
-      </c>
-      <c r="N2" s="4">
-        <v>5</v>
-      </c>
       <c r="O2" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P2" s="4">
+        <v>4</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>4</v>
+      </c>
+      <c r="R2" s="4">
+        <v>4</v>
+      </c>
+      <c r="S2" s="4">
+        <v>5</v>
+      </c>
+      <c r="T2" s="4">
+        <v>0</v>
+      </c>
+      <c r="U2" s="4">
         <v>6</v>
       </c>
-      <c r="Q2" s="4">
-        <v>4</v>
-      </c>
-      <c r="R2" s="4">
-        <v>4</v>
-      </c>
-      <c r="S2" s="4">
-        <v>4</v>
-      </c>
-      <c r="T2" s="4">
-        <v>4</v>
-      </c>
-      <c r="U2" s="4">
-        <v>5</v>
-      </c>
       <c r="V2" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W2" s="4">
+        <v>4</v>
+      </c>
+      <c r="X2" s="4">
+        <v>4</v>
+      </c>
+      <c r="Y2" s="4">
+        <v>4</v>
+      </c>
+      <c r="Z2" s="4">
+        <v>5</v>
+      </c>
+      <c r="AA2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="4">
         <v>6</v>
       </c>
-      <c r="X2" s="4">
-        <v>4</v>
-      </c>
-      <c r="Y2" s="4">
-        <v>4</v>
-      </c>
-      <c r="Z2" s="4">
-        <v>4</v>
-      </c>
-      <c r="AA2" s="4">
-        <v>4</v>
-      </c>
-      <c r="AB2" s="4">
-        <v>5</v>
-      </c>
       <c r="AC2" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD2" s="4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE2" s="4">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="AF2" s="4">
+        <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C3" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" s="4">
         <v>4</v>
       </c>
       <c r="F3" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G3" s="4">
         <v>5</v>
       </c>
       <c r="H3" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J3" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K3" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L3" s="4">
         <v>4</v>
       </c>
       <c r="M3" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N3" s="4">
         <v>5</v>
       </c>
       <c r="O3" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P3" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q3" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R3" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S3" s="4">
         <v>4</v>
       </c>
       <c r="T3" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U3" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V3" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W3" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X3" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y3" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z3" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA3" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB3" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AC3" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD3" s="4">
         <v>4</v>
       </c>
       <c r="AE3" s="4">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="AF3" s="4">
+        <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="4">
+        <v>4</v>
+      </c>
+      <c r="C4" s="4">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4">
+        <v>4</v>
+      </c>
+      <c r="E4" s="4">
+        <v>5</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4">
+        <v>5</v>
+      </c>
+      <c r="H4" s="4">
+        <v>4</v>
+      </c>
+      <c r="I4" s="4">
+        <v>4</v>
+      </c>
+      <c r="J4" s="4">
+        <v>4</v>
+      </c>
+      <c r="K4" s="4">
+        <v>4</v>
+      </c>
+      <c r="L4" s="4">
+        <v>5</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>5</v>
+      </c>
+      <c r="O4" s="4">
+        <v>4</v>
+      </c>
+      <c r="P4" s="4">
+        <v>4</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>4</v>
+      </c>
+      <c r="R4" s="4">
+        <v>4</v>
+      </c>
+      <c r="S4" s="4">
+        <v>5</v>
+      </c>
+      <c r="T4" s="4">
+        <v>0</v>
+      </c>
+      <c r="U4" s="4">
+        <v>5</v>
+      </c>
+      <c r="V4" s="4">
+        <v>4</v>
+      </c>
+      <c r="W4" s="4">
+        <v>4</v>
+      </c>
+      <c r="X4" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y4" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z4" s="4">
+        <v>4</v>
+      </c>
+      <c r="AA4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="4">
+        <v>4</v>
+      </c>
+      <c r="AC4" s="4">
+        <v>3</v>
+      </c>
+      <c r="AD4" s="4">
+        <v>3</v>
+      </c>
+      <c r="AE4" s="4">
+        <v>3</v>
+      </c>
+      <c r="AF4" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4">
+        <v>4</v>
+      </c>
+      <c r="E5" s="4">
+        <v>5</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4">
         <v>6</v>
       </c>
-      <c r="C4" s="4">
-        <v>4</v>
-      </c>
-      <c r="D4" s="4">
-        <v>4</v>
-      </c>
-      <c r="E4" s="4">
-        <v>4</v>
-      </c>
-      <c r="F4" s="4">
-        <v>4</v>
-      </c>
-      <c r="G4" s="4">
-        <v>5</v>
-      </c>
-      <c r="H4" s="4">
-        <v>0</v>
-      </c>
-      <c r="I4" s="4">
+      <c r="H5" s="4">
+        <v>4</v>
+      </c>
+      <c r="I5" s="4">
+        <v>4</v>
+      </c>
+      <c r="J5" s="4">
+        <v>4</v>
+      </c>
+      <c r="K5" s="4">
+        <v>4</v>
+      </c>
+      <c r="L5" s="4">
+        <v>5</v>
+      </c>
+      <c r="M5" s="4">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
         <v>6</v>
       </c>
-      <c r="J4" s="4">
-        <v>4</v>
-      </c>
-      <c r="K4" s="4">
-        <v>4</v>
-      </c>
-      <c r="L4" s="4">
-        <v>4</v>
-      </c>
-      <c r="M4" s="4">
-        <v>4</v>
-      </c>
-      <c r="N4" s="4">
-        <v>5</v>
-      </c>
-      <c r="O4" s="4">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4">
+      <c r="O5" s="4">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>4</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>4</v>
+      </c>
+      <c r="R5" s="4">
+        <v>4</v>
+      </c>
+      <c r="S5" s="4">
+        <v>5</v>
+      </c>
+      <c r="T5" s="4">
+        <v>0</v>
+      </c>
+      <c r="U5" s="4">
         <v>6</v>
       </c>
-      <c r="Q4" s="4">
-        <v>4</v>
-      </c>
-      <c r="R4" s="4">
-        <v>4</v>
-      </c>
-      <c r="S4" s="4">
-        <v>4</v>
-      </c>
-      <c r="T4" s="4">
-        <v>4</v>
-      </c>
-      <c r="U4" s="4">
-        <v>5</v>
-      </c>
-      <c r="V4" s="4">
-        <v>0</v>
-      </c>
-      <c r="W4" s="4">
-        <v>4</v>
-      </c>
-      <c r="X4" s="4">
-        <v>3</v>
-      </c>
-      <c r="Y4" s="4">
-        <v>3</v>
-      </c>
-      <c r="Z4" s="4">
-        <v>3</v>
-      </c>
-      <c r="AA4" s="4">
-        <v>3</v>
-      </c>
-      <c r="AB4" s="4">
-        <v>4</v>
-      </c>
-      <c r="AC4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="4">
-        <v>4</v>
-      </c>
-      <c r="AE4" s="4">
+      <c r="V5" s="4">
+        <v>4</v>
+      </c>
+      <c r="W5" s="4">
+        <v>4</v>
+      </c>
+      <c r="X5" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y5" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z5" s="4">
+        <v>4</v>
+      </c>
+      <c r="AA5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="4">
+        <v>5</v>
+      </c>
+      <c r="AC5" s="4">
+        <v>3</v>
+      </c>
+      <c r="AD5" s="4">
+        <v>3</v>
+      </c>
+      <c r="AE5" s="4">
+        <v>3</v>
+      </c>
+      <c r="AF5" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
-      <c r="A5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4">
-        <v>6</v>
-      </c>
-      <c r="C5" s="4">
-        <v>4</v>
-      </c>
-      <c r="D5" s="4">
-        <v>4</v>
-      </c>
-      <c r="E5" s="4">
-        <v>4</v>
-      </c>
-      <c r="F5" s="4">
-        <v>4</v>
-      </c>
-      <c r="G5" s="4">
-        <v>5</v>
-      </c>
-      <c r="H5" s="4">
-        <v>0</v>
-      </c>
-      <c r="I5" s="4">
-        <v>6</v>
-      </c>
-      <c r="J5" s="4">
-        <v>4</v>
-      </c>
-      <c r="K5" s="4">
-        <v>4</v>
-      </c>
-      <c r="L5" s="4">
-        <v>4</v>
-      </c>
-      <c r="M5" s="4">
-        <v>4</v>
-      </c>
-      <c r="N5" s="4">
-        <v>5</v>
-      </c>
-      <c r="O5" s="4">
-        <v>0</v>
-      </c>
-      <c r="P5" s="4">
-        <v>6</v>
-      </c>
-      <c r="Q5" s="4">
-        <v>4</v>
-      </c>
-      <c r="R5" s="4">
-        <v>4</v>
-      </c>
-      <c r="S5" s="4">
-        <v>4</v>
-      </c>
-      <c r="T5" s="4">
-        <v>4</v>
-      </c>
-      <c r="U5" s="4">
-        <v>5</v>
-      </c>
-      <c r="V5" s="4">
-        <v>0</v>
-      </c>
-      <c r="W5" s="4">
-        <v>6</v>
-      </c>
-      <c r="X5" s="4">
-        <v>4</v>
-      </c>
-      <c r="Y5" s="4">
-        <v>3</v>
-      </c>
-      <c r="Z5" s="4">
-        <v>3</v>
-      </c>
-      <c r="AA5" s="4">
-        <v>3</v>
-      </c>
-      <c r="AB5" s="4">
-        <v>4</v>
-      </c>
-      <c r="AC5" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="4">
-        <v>5</v>
-      </c>
-      <c r="AE5" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="4">
+        <v>5</v>
+      </c>
+      <c r="C6" s="4">
+        <v>5</v>
+      </c>
+      <c r="D6" s="4">
+        <v>5</v>
+      </c>
+      <c r="E6" s="4">
+        <v>6</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4">
         <v>7</v>
       </c>
-      <c r="C6" s="4">
-        <v>5</v>
-      </c>
-      <c r="D6" s="4">
-        <v>5</v>
-      </c>
-      <c r="E6" s="4">
-        <v>5</v>
-      </c>
-      <c r="F6" s="4">
-        <v>5</v>
-      </c>
-      <c r="G6" s="4">
+      <c r="H6" s="4">
+        <v>5</v>
+      </c>
+      <c r="I6" s="4">
+        <v>5</v>
+      </c>
+      <c r="J6" s="4">
+        <v>5</v>
+      </c>
+      <c r="K6" s="4">
+        <v>5</v>
+      </c>
+      <c r="L6" s="4">
         <v>6</v>
       </c>
-      <c r="H6" s="4">
-        <v>0</v>
-      </c>
-      <c r="I6" s="4">
+      <c r="M6" s="4">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
         <v>7</v>
       </c>
-      <c r="J6" s="4">
-        <v>5</v>
-      </c>
-      <c r="K6" s="4">
-        <v>5</v>
-      </c>
-      <c r="L6" s="4">
-        <v>5</v>
-      </c>
-      <c r="M6" s="4">
-        <v>5</v>
-      </c>
-      <c r="N6" s="4">
+      <c r="O6" s="4">
+        <v>5</v>
+      </c>
+      <c r="P6" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>5</v>
+      </c>
+      <c r="R6" s="4">
+        <v>5</v>
+      </c>
+      <c r="S6" s="4">
         <v>6</v>
       </c>
-      <c r="O6" s="4">
-        <v>0</v>
-      </c>
-      <c r="P6" s="4">
+      <c r="T6" s="4">
+        <v>0</v>
+      </c>
+      <c r="U6" s="4">
         <v>7</v>
       </c>
-      <c r="Q6" s="4">
-        <v>5</v>
-      </c>
-      <c r="R6" s="4">
-        <v>5</v>
-      </c>
-      <c r="S6" s="4">
-        <v>5</v>
-      </c>
-      <c r="T6" s="4">
-        <v>5</v>
-      </c>
-      <c r="U6" s="4">
+      <c r="V6" s="4">
+        <v>5</v>
+      </c>
+      <c r="W6" s="4">
+        <v>5</v>
+      </c>
+      <c r="X6" s="4">
+        <v>5</v>
+      </c>
+      <c r="Y6" s="4">
+        <v>5</v>
+      </c>
+      <c r="Z6" s="4">
+        <v>5</v>
+      </c>
+      <c r="AA6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="4">
         <v>6</v>
       </c>
-      <c r="V6" s="4">
-        <v>0</v>
-      </c>
-      <c r="W6" s="4">
-        <v>7</v>
-      </c>
-      <c r="X6" s="4">
-        <v>5</v>
-      </c>
-      <c r="Y6" s="4">
-        <v>5</v>
-      </c>
-      <c r="Z6" s="4">
-        <v>5</v>
-      </c>
-      <c r="AA6" s="4">
-        <v>5</v>
-      </c>
-      <c r="AB6" s="4">
-        <v>5</v>
-      </c>
       <c r="AC6" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD6" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE6" s="4">
         <v>4</v>
       </c>
+      <c r="AF6" s="4">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C7" s="4">
         <v>4</v>
@@ -2707,19 +2759,19 @@
         <v>4</v>
       </c>
       <c r="E7" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G7" s="4">
         <v>5</v>
       </c>
       <c r="H7" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I7" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J7" s="4">
         <v>4</v>
@@ -2728,19 +2780,19 @@
         <v>4</v>
       </c>
       <c r="L7" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M7" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N7" s="4">
         <v>5</v>
       </c>
       <c r="O7" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P7" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q7" s="4">
         <v>4</v>
@@ -2749,51 +2801,54 @@
         <v>4</v>
       </c>
       <c r="S7" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U7" s="4">
         <v>5</v>
       </c>
       <c r="V7" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W7" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X7" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y7" s="4">
         <v>3</v>
       </c>
       <c r="Z7" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA7" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="4">
         <v>4</v>
       </c>
       <c r="AC7" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD7" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE7" s="4">
         <v>3</v>
       </c>
+      <c r="AF7" s="4">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C8" s="4">
         <v>3</v>
@@ -2802,19 +2857,19 @@
         <v>3</v>
       </c>
       <c r="E8" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G8" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H8" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J8" s="4">
         <v>3</v>
@@ -2823,19 +2878,19 @@
         <v>3</v>
       </c>
       <c r="L8" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M8" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O8" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P8" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q8" s="4">
         <v>3</v>
@@ -2844,51 +2899,54 @@
         <v>3</v>
       </c>
       <c r="S8" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T8" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U8" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V8" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W8" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X8" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y8" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z8" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA8" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC8" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD8" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE8" s="4">
         <v>4</v>
       </c>
+      <c r="AF8" s="4">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B9" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" s="4">
         <v>3</v>
@@ -2900,16 +2958,16 @@
         <v>3</v>
       </c>
       <c r="F9" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G9" s="4">
         <v>4</v>
       </c>
       <c r="H9" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J9" s="4">
         <v>3</v>
@@ -2921,16 +2979,16 @@
         <v>3</v>
       </c>
       <c r="M9" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N9" s="4">
         <v>4</v>
       </c>
       <c r="O9" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P9" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q9" s="4">
         <v>3</v>
@@ -2942,16 +3000,16 @@
         <v>3</v>
       </c>
       <c r="T9" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U9" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V9" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W9" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X9" s="4">
         <v>3</v>
@@ -2960,30 +3018,33 @@
         <v>3</v>
       </c>
       <c r="Z9" s="4">
+        <v>3</v>
+      </c>
+      <c r="AA9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="4">
+        <v>3</v>
+      </c>
+      <c r="AC9" s="4">
         <v>2</v>
       </c>
-      <c r="AA9" s="4">
+      <c r="AD9" s="4">
         <v>2</v>
-      </c>
-      <c r="AB9" s="4">
-        <v>2</v>
-      </c>
-      <c r="AC9" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="4">
-        <v>3</v>
       </c>
       <c r="AE9" s="4">
         <v>2</v>
       </c>
+      <c r="AF9" s="4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10" s="4">
         <v>3</v>
@@ -2992,19 +3053,19 @@
         <v>3</v>
       </c>
       <c r="E10" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G10" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H10" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J10" s="4">
         <v>3</v>
@@ -3013,19 +3074,19 @@
         <v>3</v>
       </c>
       <c r="L10" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M10" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O10" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P10" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q10" s="4">
         <v>3</v>
@@ -3034,42 +3095,45 @@
         <v>3</v>
       </c>
       <c r="S10" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T10" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U10" s="4">
         <v>5</v>
       </c>
       <c r="V10" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W10" s="4">
+        <v>4</v>
+      </c>
+      <c r="X10" s="4">
+        <v>4</v>
+      </c>
+      <c r="Y10" s="4">
+        <v>4</v>
+      </c>
+      <c r="Z10" s="4">
+        <v>5</v>
+      </c>
+      <c r="AA10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="4">
         <v>6</v>
       </c>
-      <c r="X10" s="4">
-        <v>4</v>
-      </c>
-      <c r="Y10" s="4">
-        <v>4</v>
-      </c>
-      <c r="Z10" s="4">
-        <v>4</v>
-      </c>
-      <c r="AA10" s="4">
-        <v>4</v>
-      </c>
-      <c r="AB10" s="4">
-        <v>5</v>
-      </c>
       <c r="AC10" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD10" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE10" s="4">
+        <v>4</v>
+      </c>
+      <c r="AF10" s="4">
         <v>4</v>
       </c>
     </row>

--- a/target.xlsx
+++ b/target.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\백업폴더\딱따구리\AI\강북도매 영업관리 포털\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F2FAD15-1333-4F6B-AA80-33E3A2C9249D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07991DCE-AC40-41B3-A7F6-75E1B8A488D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F51F585E-D8DA-4EE1-A615-D4BBA305B88C}"/>
   </bookViews>
@@ -1327,7 +1327,7 @@
         <v>17</v>
       </c>
       <c r="X2" s="7">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y2" s="7">
         <v>18</v>
@@ -1386,7 +1386,7 @@
         <v>13</v>
       </c>
       <c r="K3" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L3" s="7">
         <v>19</v>
@@ -1466,13 +1466,13 @@
         <v>19</v>
       </c>
       <c r="E4" s="7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" s="7">
         <v>0</v>
       </c>
       <c r="G4" s="7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H4" s="7">
         <v>19</v>
@@ -1487,13 +1487,13 @@
         <v>19</v>
       </c>
       <c r="L4" s="7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M4" s="7">
         <v>0</v>
       </c>
       <c r="N4" s="7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O4" s="7">
         <v>19</v>
@@ -1508,34 +1508,34 @@
         <v>19</v>
       </c>
       <c r="S4" s="7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T4" s="7">
         <v>0</v>
       </c>
       <c r="U4" s="7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="V4" s="7">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="W4" s="7">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="X4" s="7">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y4" s="7">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z4" s="7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA4" s="7">
         <v>0</v>
       </c>
       <c r="AB4" s="7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AC4" s="7">
         <v>20</v>
@@ -1645,7 +1645,7 @@
         <v>20</v>
       </c>
       <c r="AF5" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.45">
@@ -1683,16 +1683,16 @@
         <v>23</v>
       </c>
       <c r="L6" s="7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M6" s="7">
         <v>0</v>
       </c>
       <c r="N6" s="7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O6" s="7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P6" s="7">
         <v>24</v>
@@ -1796,10 +1796,10 @@
         <v>16</v>
       </c>
       <c r="Q7" s="7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R7" s="7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S7" s="7">
         <v>22</v>
@@ -1891,10 +1891,10 @@
         <v>14</v>
       </c>
       <c r="P8" s="7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q8" s="7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R8" s="7">
         <v>15</v>
@@ -2007,10 +2007,10 @@
         <v>24</v>
       </c>
       <c r="V9" s="7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W9" s="7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="X9" s="7">
         <v>17</v>
@@ -2105,10 +2105,10 @@
         <v>23</v>
       </c>
       <c r="V10" s="7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W10" s="7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X10" s="7">
         <v>16</v>
@@ -2350,7 +2350,7 @@
         <v>4</v>
       </c>
       <c r="AF2" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.45">
@@ -2448,7 +2448,7 @@
         <v>4</v>
       </c>
       <c r="AF3" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.45">
@@ -2522,7 +2522,7 @@
         <v>4</v>
       </c>
       <c r="X4" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y4" s="4">
         <v>3</v>
@@ -2617,7 +2617,7 @@
         <v>4</v>
       </c>
       <c r="W5" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X5" s="4">
         <v>3</v>
@@ -2724,7 +2724,7 @@
         <v>5</v>
       </c>
       <c r="Z6" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA6" s="4">
         <v>0</v>
@@ -2920,7 +2920,7 @@
         <v>3</v>
       </c>
       <c r="Z8" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA8" s="4">
         <v>0</v>
@@ -3024,7 +3024,7 @@
         <v>0</v>
       </c>
       <c r="AB9" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC9" s="4">
         <v>2</v>
@@ -3134,7 +3134,7 @@
         <v>4</v>
       </c>
       <c r="AF10" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/target.xlsx
+++ b/target.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\백업폴더\딱따구리\AI\강북도매 영업관리 포털\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07991DCE-AC40-41B3-A7F6-75E1B8A488D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3853FF1D-C8A1-4778-8476-CF664F359F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F51F585E-D8DA-4EE1-A615-D4BBA305B88C}"/>
   </bookViews>
@@ -1163,97 +1163,97 @@
         <v>9</v>
       </c>
       <c r="B1" s="6">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="C1" s="6">
-        <v>46205</v>
+        <v>46236</v>
       </c>
       <c r="D1" s="6">
-        <v>46206</v>
+        <v>46237</v>
       </c>
       <c r="E1" s="6">
-        <v>46207</v>
+        <v>46238</v>
       </c>
       <c r="F1" s="6">
-        <v>46208</v>
+        <v>46239</v>
       </c>
       <c r="G1" s="6">
-        <v>46209</v>
+        <v>46240</v>
       </c>
       <c r="H1" s="6">
-        <v>46210</v>
+        <v>46241</v>
       </c>
       <c r="I1" s="6">
-        <v>46211</v>
+        <v>46242</v>
       </c>
       <c r="J1" s="6">
-        <v>46212</v>
+        <v>46243</v>
       </c>
       <c r="K1" s="6">
-        <v>46213</v>
+        <v>46244</v>
       </c>
       <c r="L1" s="6">
-        <v>46214</v>
+        <v>46245</v>
       </c>
       <c r="M1" s="6">
-        <v>46215</v>
+        <v>46246</v>
       </c>
       <c r="N1" s="6">
-        <v>46216</v>
+        <v>46247</v>
       </c>
       <c r="O1" s="6">
-        <v>46217</v>
+        <v>46248</v>
       </c>
       <c r="P1" s="6">
-        <v>46218</v>
+        <v>46249</v>
       </c>
       <c r="Q1" s="6">
-        <v>46219</v>
+        <v>46250</v>
       </c>
       <c r="R1" s="6">
-        <v>46220</v>
+        <v>46251</v>
       </c>
       <c r="S1" s="6">
-        <v>46221</v>
+        <v>46252</v>
       </c>
       <c r="T1" s="6">
-        <v>46222</v>
+        <v>46253</v>
       </c>
       <c r="U1" s="6">
-        <v>46223</v>
+        <v>46254</v>
       </c>
       <c r="V1" s="6">
-        <v>46224</v>
+        <v>46255</v>
       </c>
       <c r="W1" s="6">
-        <v>46225</v>
+        <v>46256</v>
       </c>
       <c r="X1" s="6">
-        <v>46226</v>
+        <v>46257</v>
       </c>
       <c r="Y1" s="6">
-        <v>46227</v>
+        <v>46258</v>
       </c>
       <c r="Z1" s="6">
-        <v>46228</v>
+        <v>46259</v>
       </c>
       <c r="AA1" s="6">
-        <v>46229</v>
+        <v>46260</v>
       </c>
       <c r="AB1" s="6">
-        <v>46230</v>
+        <v>46261</v>
       </c>
       <c r="AC1" s="6">
-        <v>46231</v>
+        <v>46262</v>
       </c>
       <c r="AD1" s="6">
-        <v>46232</v>
+        <v>46263</v>
       </c>
       <c r="AE1" s="6">
-        <v>46233</v>
+        <v>46264</v>
       </c>
       <c r="AF1" s="6">
-        <v>46234</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.45">
@@ -1261,97 +1261,97 @@
         <v>0</v>
       </c>
       <c r="B2" s="7">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C2" s="7">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D2" s="7">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E2" s="7">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F2" s="7">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G2" s="7">
+        <v>18</v>
+      </c>
+      <c r="H2" s="7">
+        <v>18</v>
+      </c>
+      <c r="I2" s="7">
+        <v>24</v>
+      </c>
+      <c r="J2" s="7">
+        <v>0</v>
+      </c>
+      <c r="K2" s="7">
+        <v>27</v>
+      </c>
+      <c r="L2" s="7">
+        <v>18</v>
+      </c>
+      <c r="M2" s="7">
+        <v>18</v>
+      </c>
+      <c r="N2" s="7">
+        <v>18</v>
+      </c>
+      <c r="O2" s="7">
+        <v>18</v>
+      </c>
+      <c r="P2" s="7">
+        <v>24</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7">
+        <v>27</v>
+      </c>
+      <c r="S2" s="7">
+        <v>18</v>
+      </c>
+      <c r="T2" s="7">
+        <v>18</v>
+      </c>
+      <c r="U2" s="7">
+        <v>19</v>
+      </c>
+      <c r="V2" s="7">
+        <v>19</v>
+      </c>
+      <c r="W2" s="7">
         <v>25</v>
       </c>
-      <c r="H2" s="7">
-        <v>17</v>
-      </c>
-      <c r="I2" s="7">
-        <v>17</v>
-      </c>
-      <c r="J2" s="7">
-        <v>17</v>
-      </c>
-      <c r="K2" s="7">
-        <v>17</v>
-      </c>
-      <c r="L2" s="7">
-        <v>22</v>
-      </c>
-      <c r="M2" s="7">
-        <v>0</v>
-      </c>
-      <c r="N2" s="7">
+      <c r="X2" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="7">
+        <v>29</v>
+      </c>
+      <c r="Z2" s="7">
+        <v>20</v>
+      </c>
+      <c r="AA2" s="7">
+        <v>20</v>
+      </c>
+      <c r="AB2" s="7">
+        <v>20</v>
+      </c>
+      <c r="AC2" s="7">
+        <v>20</v>
+      </c>
+      <c r="AD2" s="7">
         <v>25</v>
       </c>
-      <c r="O2" s="7">
-        <v>17</v>
-      </c>
-      <c r="P2" s="7">
-        <v>17</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>17</v>
-      </c>
-      <c r="R2" s="7">
-        <v>17</v>
-      </c>
-      <c r="S2" s="7">
-        <v>22</v>
-      </c>
-      <c r="T2" s="7">
-        <v>0</v>
-      </c>
-      <c r="U2" s="7">
-        <v>25</v>
-      </c>
-      <c r="V2" s="7">
-        <v>17</v>
-      </c>
-      <c r="W2" s="7">
-        <v>17</v>
-      </c>
-      <c r="X2" s="7">
-        <v>17</v>
-      </c>
-      <c r="Y2" s="7">
-        <v>18</v>
-      </c>
-      <c r="Z2" s="7">
-        <v>23</v>
-      </c>
-      <c r="AA2" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="7">
-        <v>26</v>
-      </c>
-      <c r="AC2" s="7">
-        <v>18</v>
-      </c>
-      <c r="AD2" s="7">
-        <v>18</v>
-      </c>
       <c r="AE2" s="7">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AF2" s="7">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.45">
@@ -1359,97 +1359,97 @@
         <v>2</v>
       </c>
       <c r="B3" s="7">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C3" s="7">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D3" s="7">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E3" s="7">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F3" s="7">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G3" s="7">
+        <v>15</v>
+      </c>
+      <c r="H3" s="7">
+        <v>15</v>
+      </c>
+      <c r="I3" s="7">
+        <v>19</v>
+      </c>
+      <c r="J3" s="7">
+        <v>0</v>
+      </c>
+      <c r="K3" s="7">
+        <v>22</v>
+      </c>
+      <c r="L3" s="7">
+        <v>15</v>
+      </c>
+      <c r="M3" s="7">
+        <v>15</v>
+      </c>
+      <c r="N3" s="7">
+        <v>15</v>
+      </c>
+      <c r="O3" s="7">
+        <v>15</v>
+      </c>
+      <c r="P3" s="7">
+        <v>19</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>0</v>
+      </c>
+      <c r="R3" s="7">
+        <v>22</v>
+      </c>
+      <c r="S3" s="7">
+        <v>15</v>
+      </c>
+      <c r="T3" s="7">
+        <v>15</v>
+      </c>
+      <c r="U3" s="7">
+        <v>15</v>
+      </c>
+      <c r="V3" s="7">
+        <v>16</v>
+      </c>
+      <c r="W3" s="7">
+        <v>20</v>
+      </c>
+      <c r="X3" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="7">
+        <v>24</v>
+      </c>
+      <c r="Z3" s="7">
+        <v>16</v>
+      </c>
+      <c r="AA3" s="7">
+        <v>16</v>
+      </c>
+      <c r="AB3" s="7">
+        <v>16</v>
+      </c>
+      <c r="AC3" s="7">
+        <v>16</v>
+      </c>
+      <c r="AD3" s="7">
         <v>21</v>
       </c>
-      <c r="H3" s="7">
-        <v>13</v>
-      </c>
-      <c r="I3" s="7">
-        <v>13</v>
-      </c>
-      <c r="J3" s="7">
-        <v>13</v>
-      </c>
-      <c r="K3" s="7">
-        <v>14</v>
-      </c>
-      <c r="L3" s="7">
-        <v>19</v>
-      </c>
-      <c r="M3" s="7">
-        <v>0</v>
-      </c>
-      <c r="N3" s="7">
-        <v>22</v>
-      </c>
-      <c r="O3" s="7">
-        <v>14</v>
-      </c>
-      <c r="P3" s="7">
-        <v>14</v>
-      </c>
-      <c r="Q3" s="7">
-        <v>14</v>
-      </c>
-      <c r="R3" s="7">
-        <v>14</v>
-      </c>
-      <c r="S3" s="7">
-        <v>19</v>
-      </c>
-      <c r="T3" s="7">
-        <v>0</v>
-      </c>
-      <c r="U3" s="7">
-        <v>22</v>
-      </c>
-      <c r="V3" s="7">
-        <v>14</v>
-      </c>
-      <c r="W3" s="7">
-        <v>14</v>
-      </c>
-      <c r="X3" s="7">
-        <v>14</v>
-      </c>
-      <c r="Y3" s="7">
-        <v>14</v>
-      </c>
-      <c r="Z3" s="7">
-        <v>19</v>
-      </c>
-      <c r="AA3" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="7">
-        <v>22</v>
-      </c>
-      <c r="AC3" s="7">
-        <v>14</v>
-      </c>
-      <c r="AD3" s="7">
-        <v>14</v>
-      </c>
       <c r="AE3" s="7">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AF3" s="7">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.45">
@@ -1457,97 +1457,97 @@
         <v>1</v>
       </c>
       <c r="B4" s="7">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C4" s="7">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D4" s="7">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E4" s="7">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F4" s="7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G4" s="7">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H4" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I4" s="7">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J4" s="7">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K4" s="7">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L4" s="7">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M4" s="7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N4" s="7">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="O4" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P4" s="7">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="Q4" s="7">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="R4" s="7">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="S4" s="7">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="T4" s="7">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="U4" s="7">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="V4" s="7">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="W4" s="7">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="X4" s="7">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="7">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="Z4" s="7">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AA4" s="7">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AB4" s="7">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AC4" s="7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AD4" s="7">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AE4" s="7">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AF4" s="7">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.45">
@@ -1555,97 +1555,97 @@
         <v>4</v>
       </c>
       <c r="B5" s="7">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C5" s="7">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D5" s="7">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E5" s="7">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F5" s="7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G5" s="7">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H5" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I5" s="7">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J5" s="7">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K5" s="7">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="L5" s="7">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="M5" s="7">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="N5" s="7">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="O5" s="7">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P5" s="7">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="Q5" s="7">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="R5" s="7">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="S5" s="7">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="T5" s="7">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="U5" s="7">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="V5" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W5" s="7">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="X5" s="7">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="7">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="Z5" s="7">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AA5" s="7">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AB5" s="7">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AC5" s="7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AD5" s="7">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AE5" s="7">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AF5" s="7">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.45">
@@ -1653,97 +1653,97 @@
         <v>8</v>
       </c>
       <c r="B6" s="7">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C6" s="7">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D6" s="7">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="E6" s="7">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F6" s="7">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G6" s="7">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H6" s="7">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I6" s="7">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="J6" s="7">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K6" s="7">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="L6" s="7">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="M6" s="7">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N6" s="7">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="O6" s="7">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P6" s="7">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="Q6" s="7">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R6" s="7">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="S6" s="7">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="T6" s="7">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="U6" s="7">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="V6" s="7">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="W6" s="7">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="X6" s="7">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="7">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="Z6" s="7">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AA6" s="7">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AB6" s="7">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="AC6" s="7">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AD6" s="7">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="AE6" s="7">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AF6" s="7">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.45">
@@ -1751,97 +1751,97 @@
         <v>3</v>
       </c>
       <c r="B7" s="7">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C7" s="7">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D7" s="7">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E7" s="7">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F7" s="7">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G7" s="7">
+        <v>17</v>
+      </c>
+      <c r="H7" s="7">
+        <v>17</v>
+      </c>
+      <c r="I7" s="7">
+        <v>23</v>
+      </c>
+      <c r="J7" s="7">
+        <v>0</v>
+      </c>
+      <c r="K7" s="7">
+        <v>26</v>
+      </c>
+      <c r="L7" s="7">
+        <v>17</v>
+      </c>
+      <c r="M7" s="7">
+        <v>17</v>
+      </c>
+      <c r="N7" s="7">
+        <v>17</v>
+      </c>
+      <c r="O7" s="7">
+        <v>17</v>
+      </c>
+      <c r="P7" s="7">
+        <v>23</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>0</v>
+      </c>
+      <c r="R7" s="7">
+        <v>27</v>
+      </c>
+      <c r="S7" s="7">
+        <v>18</v>
+      </c>
+      <c r="T7" s="7">
+        <v>18</v>
+      </c>
+      <c r="U7" s="7">
+        <v>18</v>
+      </c>
+      <c r="V7" s="7">
+        <v>18</v>
+      </c>
+      <c r="W7" s="7">
         <v>24</v>
       </c>
-      <c r="H7" s="7">
-        <v>16</v>
-      </c>
-      <c r="I7" s="7">
-        <v>16</v>
-      </c>
-      <c r="J7" s="7">
-        <v>16</v>
-      </c>
-      <c r="K7" s="7">
-        <v>16</v>
-      </c>
-      <c r="L7" s="7">
-        <v>21</v>
-      </c>
-      <c r="M7" s="7">
-        <v>0</v>
-      </c>
-      <c r="N7" s="7">
+      <c r="X7" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="7">
+        <v>28</v>
+      </c>
+      <c r="Z7" s="7">
+        <v>19</v>
+      </c>
+      <c r="AA7" s="7">
+        <v>19</v>
+      </c>
+      <c r="AB7" s="7">
+        <v>19</v>
+      </c>
+      <c r="AC7" s="7">
+        <v>19</v>
+      </c>
+      <c r="AD7" s="7">
         <v>24</v>
       </c>
-      <c r="O7" s="7">
-        <v>16</v>
-      </c>
-      <c r="P7" s="7">
-        <v>16</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>16</v>
-      </c>
-      <c r="R7" s="7">
-        <v>16</v>
-      </c>
-      <c r="S7" s="7">
-        <v>22</v>
-      </c>
-      <c r="T7" s="7">
-        <v>0</v>
-      </c>
-      <c r="U7" s="7">
-        <v>25</v>
-      </c>
-      <c r="V7" s="7">
-        <v>17</v>
-      </c>
-      <c r="W7" s="7">
-        <v>17</v>
-      </c>
-      <c r="X7" s="7">
-        <v>17</v>
-      </c>
-      <c r="Y7" s="7">
-        <v>17</v>
-      </c>
-      <c r="Z7" s="7">
-        <v>22</v>
-      </c>
-      <c r="AA7" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="7">
-        <v>25</v>
-      </c>
-      <c r="AC7" s="7">
-        <v>17</v>
-      </c>
-      <c r="AD7" s="7">
-        <v>17</v>
-      </c>
       <c r="AE7" s="7">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AF7" s="7">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.45">
@@ -1849,97 +1849,97 @@
         <v>6</v>
       </c>
       <c r="B8" s="7">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C8" s="7">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D8" s="7">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E8" s="7">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F8" s="7">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G8" s="7">
+        <v>15</v>
+      </c>
+      <c r="H8" s="7">
+        <v>15</v>
+      </c>
+      <c r="I8" s="7">
+        <v>20</v>
+      </c>
+      <c r="J8" s="7">
+        <v>0</v>
+      </c>
+      <c r="K8" s="7">
+        <v>23</v>
+      </c>
+      <c r="L8" s="7">
+        <v>15</v>
+      </c>
+      <c r="M8" s="7">
+        <v>15</v>
+      </c>
+      <c r="N8" s="7">
+        <v>15</v>
+      </c>
+      <c r="O8" s="7">
+        <v>16</v>
+      </c>
+      <c r="P8" s="7">
         <v>21</v>
       </c>
-      <c r="H8" s="7">
-        <v>14</v>
-      </c>
-      <c r="I8" s="7">
-        <v>14</v>
-      </c>
-      <c r="J8" s="7">
-        <v>14</v>
-      </c>
-      <c r="K8" s="7">
-        <v>14</v>
-      </c>
-      <c r="L8" s="7">
-        <v>18</v>
-      </c>
-      <c r="M8" s="7">
-        <v>0</v>
-      </c>
-      <c r="N8" s="7">
+      <c r="Q8" s="7">
+        <v>0</v>
+      </c>
+      <c r="R8" s="7">
+        <v>24</v>
+      </c>
+      <c r="S8" s="7">
+        <v>16</v>
+      </c>
+      <c r="T8" s="7">
+        <v>16</v>
+      </c>
+      <c r="U8" s="7">
+        <v>16</v>
+      </c>
+      <c r="V8" s="7">
+        <v>16</v>
+      </c>
+      <c r="W8" s="7">
         <v>21</v>
       </c>
-      <c r="O8" s="7">
-        <v>14</v>
-      </c>
-      <c r="P8" s="7">
-        <v>14</v>
-      </c>
-      <c r="Q8" s="7">
-        <v>14</v>
-      </c>
-      <c r="R8" s="7">
-        <v>15</v>
-      </c>
-      <c r="S8" s="7">
-        <v>19</v>
-      </c>
-      <c r="T8" s="7">
-        <v>0</v>
-      </c>
-      <c r="U8" s="7">
-        <v>22</v>
-      </c>
-      <c r="V8" s="7">
-        <v>15</v>
-      </c>
-      <c r="W8" s="7">
-        <v>15</v>
-      </c>
       <c r="X8" s="7">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="7">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="Z8" s="7">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA8" s="7">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AB8" s="7">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AC8" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AD8" s="7">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AE8" s="7">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="7">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.45">
@@ -1947,97 +1947,97 @@
         <v>5</v>
       </c>
       <c r="B9" s="7">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C9" s="7">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D9" s="7">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E9" s="7">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F9" s="7">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G9" s="7">
+        <v>17</v>
+      </c>
+      <c r="H9" s="7">
+        <v>17</v>
+      </c>
+      <c r="I9" s="7">
+        <v>22</v>
+      </c>
+      <c r="J9" s="7">
+        <v>0</v>
+      </c>
+      <c r="K9" s="7">
+        <v>26</v>
+      </c>
+      <c r="L9" s="7">
+        <v>17</v>
+      </c>
+      <c r="M9" s="7">
+        <v>17</v>
+      </c>
+      <c r="N9" s="7">
+        <v>17</v>
+      </c>
+      <c r="O9" s="7">
+        <v>17</v>
+      </c>
+      <c r="P9" s="7">
+        <v>22</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>0</v>
+      </c>
+      <c r="R9" s="7">
+        <v>26</v>
+      </c>
+      <c r="S9" s="7">
+        <v>18</v>
+      </c>
+      <c r="T9" s="7">
+        <v>18</v>
+      </c>
+      <c r="U9" s="7">
+        <v>18</v>
+      </c>
+      <c r="V9" s="7">
+        <v>18</v>
+      </c>
+      <c r="W9" s="7">
+        <v>23</v>
+      </c>
+      <c r="X9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="7">
+        <v>28</v>
+      </c>
+      <c r="Z9" s="7">
+        <v>19</v>
+      </c>
+      <c r="AA9" s="7">
+        <v>19</v>
+      </c>
+      <c r="AB9" s="7">
+        <v>19</v>
+      </c>
+      <c r="AC9" s="7">
+        <v>19</v>
+      </c>
+      <c r="AD9" s="7">
         <v>24</v>
       </c>
-      <c r="H9" s="7">
-        <v>16</v>
-      </c>
-      <c r="I9" s="7">
-        <v>16</v>
-      </c>
-      <c r="J9" s="7">
-        <v>16</v>
-      </c>
-      <c r="K9" s="7">
-        <v>16</v>
-      </c>
-      <c r="L9" s="7">
-        <v>21</v>
-      </c>
-      <c r="M9" s="7">
-        <v>0</v>
-      </c>
-      <c r="N9" s="7">
-        <v>24</v>
-      </c>
-      <c r="O9" s="7">
-        <v>16</v>
-      </c>
-      <c r="P9" s="7">
-        <v>16</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>16</v>
-      </c>
-      <c r="R9" s="7">
-        <v>16</v>
-      </c>
-      <c r="S9" s="7">
-        <v>21</v>
-      </c>
-      <c r="T9" s="7">
-        <v>0</v>
-      </c>
-      <c r="U9" s="7">
-        <v>24</v>
-      </c>
-      <c r="V9" s="7">
-        <v>16</v>
-      </c>
-      <c r="W9" s="7">
-        <v>16</v>
-      </c>
-      <c r="X9" s="7">
-        <v>17</v>
-      </c>
-      <c r="Y9" s="7">
-        <v>17</v>
-      </c>
-      <c r="Z9" s="7">
-        <v>22</v>
-      </c>
-      <c r="AA9" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="7">
-        <v>25</v>
-      </c>
-      <c r="AC9" s="7">
-        <v>17</v>
-      </c>
-      <c r="AD9" s="7">
-        <v>17</v>
-      </c>
       <c r="AE9" s="7">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AF9" s="7">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.45">
@@ -2045,97 +2045,97 @@
         <v>7</v>
       </c>
       <c r="B10" s="7">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C10" s="7">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D10" s="7">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E10" s="7">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F10" s="7">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G10" s="7">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H10" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I10" s="7">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J10" s="7">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K10" s="7">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="L10" s="7">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M10" s="7">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="N10" s="7">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="O10" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P10" s="7">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q10" s="7">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R10" s="7">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="S10" s="7">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T10" s="7">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="U10" s="7">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="V10" s="7">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="W10" s="7">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="X10" s="7">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="7">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="Z10" s="7">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AA10" s="7">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AB10" s="7">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AC10" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AD10" s="7">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AE10" s="7">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AF10" s="7">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -2162,97 +2162,97 @@
         <v>9</v>
       </c>
       <c r="B1" s="2">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="C1" s="2">
-        <v>46205</v>
+        <v>46236</v>
       </c>
       <c r="D1" s="2">
-        <v>46206</v>
+        <v>46237</v>
       </c>
       <c r="E1" s="2">
-        <v>46207</v>
+        <v>46238</v>
       </c>
       <c r="F1" s="2">
-        <v>46208</v>
+        <v>46239</v>
       </c>
       <c r="G1" s="2">
-        <v>46209</v>
+        <v>46240</v>
       </c>
       <c r="H1" s="2">
-        <v>46210</v>
+        <v>46241</v>
       </c>
       <c r="I1" s="2">
-        <v>46211</v>
+        <v>46242</v>
       </c>
       <c r="J1" s="2">
-        <v>46212</v>
+        <v>46243</v>
       </c>
       <c r="K1" s="2">
-        <v>46213</v>
+        <v>46244</v>
       </c>
       <c r="L1" s="2">
-        <v>46214</v>
+        <v>46245</v>
       </c>
       <c r="M1" s="2">
-        <v>46215</v>
+        <v>46246</v>
       </c>
       <c r="N1" s="2">
-        <v>46216</v>
+        <v>46247</v>
       </c>
       <c r="O1" s="2">
-        <v>46217</v>
+        <v>46248</v>
       </c>
       <c r="P1" s="2">
-        <v>46218</v>
+        <v>46249</v>
       </c>
       <c r="Q1" s="2">
-        <v>46219</v>
+        <v>46250</v>
       </c>
       <c r="R1" s="2">
-        <v>46220</v>
+        <v>46251</v>
       </c>
       <c r="S1" s="2">
-        <v>46221</v>
+        <v>46252</v>
       </c>
       <c r="T1" s="2">
-        <v>46222</v>
+        <v>46253</v>
       </c>
       <c r="U1" s="2">
-        <v>46223</v>
+        <v>46254</v>
       </c>
       <c r="V1" s="2">
-        <v>46224</v>
+        <v>46255</v>
       </c>
       <c r="W1" s="2">
-        <v>46225</v>
+        <v>46256</v>
       </c>
       <c r="X1" s="2">
-        <v>46226</v>
+        <v>46257</v>
       </c>
       <c r="Y1" s="2">
-        <v>46227</v>
+        <v>46258</v>
       </c>
       <c r="Z1" s="2">
-        <v>46228</v>
+        <v>46259</v>
       </c>
       <c r="AA1" s="2">
-        <v>46229</v>
+        <v>46260</v>
       </c>
       <c r="AB1" s="2">
-        <v>46230</v>
+        <v>46261</v>
       </c>
       <c r="AC1" s="2">
-        <v>46231</v>
+        <v>46262</v>
       </c>
       <c r="AD1" s="2">
-        <v>46232</v>
+        <v>46263</v>
       </c>
       <c r="AE1" s="2">
-        <v>46233</v>
+        <v>46264</v>
       </c>
       <c r="AF1" s="2">
-        <v>46234</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.45">
@@ -2260,97 +2260,97 @@
         <v>0</v>
       </c>
       <c r="B2" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C2" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D2" s="4">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E2" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2" s="4">
         <v>6</v>
       </c>
       <c r="H2" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I2" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J2" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K2" s="4">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L2" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M2" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N2" s="4">
         <v>6</v>
       </c>
       <c r="O2" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P2" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q2" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R2" s="4">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="S2" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T2" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U2" s="4">
         <v>6</v>
       </c>
       <c r="V2" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W2" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="X2" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="4">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Z2" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA2" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB2" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC2" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AD2" s="4">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE2" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AF2" s="4">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.45">
@@ -2358,97 +2358,97 @@
         <v>2</v>
       </c>
       <c r="B3" s="4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C3" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D3" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E3" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G3" s="4">
         <v>5</v>
       </c>
       <c r="H3" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I3" s="4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J3" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L3" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M3" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N3" s="4">
         <v>5</v>
       </c>
       <c r="O3" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q3" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R3" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S3" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T3" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U3" s="4">
         <v>5</v>
       </c>
       <c r="V3" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W3" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="X3" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z3" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA3" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB3" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC3" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AD3" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE3" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AF3" s="4">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.45">
@@ -2456,97 +2456,97 @@
         <v>1</v>
       </c>
       <c r="B4" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D4" s="4">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E4" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G4" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H4" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I4" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J4" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K4" s="4">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L4" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N4" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O4" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q4" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R4" s="4">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="S4" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T4" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U4" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V4" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W4" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="X4" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="4">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Z4" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA4" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB4" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AC4" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD4" s="4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE4" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF4" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.45">
@@ -2554,97 +2554,97 @@
         <v>4</v>
       </c>
       <c r="B5" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C5" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D5" s="4">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E5" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G5" s="4">
         <v>6</v>
       </c>
       <c r="H5" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I5" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J5" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K5" s="4">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L5" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M5" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N5" s="4">
         <v>6</v>
       </c>
       <c r="O5" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q5" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R5" s="4">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="S5" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T5" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U5" s="4">
         <v>6</v>
       </c>
       <c r="V5" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W5" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="X5" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="4">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Z5" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA5" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB5" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC5" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD5" s="4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE5" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF5" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.45">
@@ -2652,97 +2652,97 @@
         <v>8</v>
       </c>
       <c r="B6" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C6" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D6" s="4">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E6" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" s="4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G6" s="4">
         <v>7</v>
       </c>
       <c r="H6" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I6" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J6" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K6" s="4">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L6" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M6" s="4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N6" s="4">
         <v>7</v>
       </c>
       <c r="O6" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P6" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q6" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R6" s="4">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="S6" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T6" s="4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U6" s="4">
         <v>7</v>
       </c>
       <c r="V6" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W6" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="X6" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="4">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Z6" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA6" s="4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AB6" s="4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AC6" s="4">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AD6" s="4">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AE6" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AF6" s="4">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.45">
@@ -2750,97 +2750,97 @@
         <v>3</v>
       </c>
       <c r="B7" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C7" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D7" s="4">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E7" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G7" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H7" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I7" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J7" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K7" s="4">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L7" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M7" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N7" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O7" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P7" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q7" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R7" s="4">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="S7" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T7" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U7" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V7" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W7" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="X7" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="4">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Z7" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA7" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB7" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AC7" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD7" s="4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE7" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF7" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.45">
@@ -2848,97 +2848,97 @@
         <v>6</v>
       </c>
       <c r="B8" s="4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C8" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D8" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E8" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G8" s="4">
         <v>5</v>
       </c>
       <c r="H8" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I8" s="4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J8" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K8" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L8" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M8" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N8" s="4">
         <v>5</v>
       </c>
       <c r="O8" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P8" s="4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q8" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R8" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S8" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T8" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U8" s="4">
         <v>5</v>
       </c>
       <c r="V8" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W8" s="4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="X8" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Z8" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA8" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB8" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC8" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD8" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE8" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="4">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.45">
@@ -2946,97 +2946,97 @@
         <v>5</v>
       </c>
       <c r="B9" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C9" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D9" s="4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E9" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G9" s="4">
         <v>4</v>
       </c>
       <c r="H9" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J9" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9" s="4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L9" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M9" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N9" s="4">
         <v>4</v>
       </c>
       <c r="O9" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P9" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q9" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R9" s="4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S9" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T9" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U9" s="4">
         <v>4</v>
       </c>
       <c r="V9" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W9" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="X9" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Z9" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA9" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB9" s="4">
         <v>4</v>
       </c>
       <c r="AC9" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD9" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE9" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF9" s="4">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.45">
@@ -3044,97 +3044,97 @@
         <v>7</v>
       </c>
       <c r="B10" s="4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C10" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D10" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E10" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G10" s="4">
         <v>5</v>
       </c>
       <c r="H10" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I10" s="4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J10" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K10" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L10" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M10" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N10" s="4">
         <v>5</v>
       </c>
       <c r="O10" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P10" s="4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q10" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R10" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S10" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T10" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U10" s="4">
         <v>5</v>
       </c>
       <c r="V10" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W10" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="X10" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z10" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA10" s="4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AB10" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC10" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AD10" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE10" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AF10" s="4">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/target.xlsx
+++ b/target.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\백업폴더\딱따구리\AI\강북도매 영업관리 포털\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kt\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3853FF1D-C8A1-4778-8476-CF664F359F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{315D6210-40B4-4F18-9F11-711B93D11E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F51F585E-D8DA-4EE1-A615-D4BBA305B88C}"/>
   </bookViews>
@@ -1267,19 +1267,19 @@
         <v>0</v>
       </c>
       <c r="D2" s="7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E2" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I2" s="7">
         <v>24</v>
@@ -1288,19 +1288,19 @@
         <v>0</v>
       </c>
       <c r="K2" s="7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L2" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M2" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N2" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O2" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P2" s="7">
         <v>24</v>
@@ -1309,22 +1309,22 @@
         <v>0</v>
       </c>
       <c r="R2" s="7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S2" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T2" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U2" s="7">
         <v>19</v>
       </c>
       <c r="V2" s="7">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="W2" s="7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X2" s="7">
         <v>0</v>
@@ -1333,16 +1333,16 @@
         <v>29</v>
       </c>
       <c r="Z2" s="7">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA2" s="7">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AB2" s="7">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AC2" s="7">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AD2" s="7">
         <v>25</v>
@@ -1365,7 +1365,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" s="7">
         <v>15</v>
@@ -1386,7 +1386,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L3" s="7">
         <v>15</v>
@@ -1401,13 +1401,13 @@
         <v>15</v>
       </c>
       <c r="P3" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q3" s="7">
         <v>0</v>
       </c>
       <c r="R3" s="7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S3" s="7">
         <v>15</v>
@@ -1419,7 +1419,7 @@
         <v>15</v>
       </c>
       <c r="V3" s="7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W3" s="7">
         <v>20</v>
@@ -1428,28 +1428,28 @@
         <v>0</v>
       </c>
       <c r="Y3" s="7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z3" s="7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA3" s="7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB3" s="7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC3" s="7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AD3" s="7">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE3" s="7">
         <v>0</v>
       </c>
       <c r="AF3" s="7">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.45">
@@ -1463,19 +1463,19 @@
         <v>0</v>
       </c>
       <c r="D4" s="7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G4" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H4" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I4" s="7">
         <v>27</v>
@@ -1484,22 +1484,22 @@
         <v>0</v>
       </c>
       <c r="K4" s="7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L4" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M4" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N4" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O4" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P4" s="7">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q4" s="7">
         <v>0</v>
@@ -1520,25 +1520,25 @@
         <v>21</v>
       </c>
       <c r="W4" s="7">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X4" s="7">
         <v>0</v>
       </c>
       <c r="Y4" s="7">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z4" s="7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA4" s="7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB4" s="7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC4" s="7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AD4" s="7">
         <v>28</v>
@@ -1547,7 +1547,7 @@
         <v>0</v>
       </c>
       <c r="AF4" s="7">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.45">
@@ -1561,22 +1561,22 @@
         <v>0</v>
       </c>
       <c r="D5" s="7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H5" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I5" s="7">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J5" s="7">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>21</v>
       </c>
       <c r="P5" s="7">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q5" s="7">
         <v>0</v>
@@ -1618,7 +1618,7 @@
         <v>21</v>
       </c>
       <c r="W5" s="7">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X5" s="7">
         <v>0</v>
@@ -1653,7 +1653,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" s="7">
         <v>0</v>
@@ -1662,19 +1662,19 @@
         <v>39</v>
       </c>
       <c r="E6" s="7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" s="7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G6" s="7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H6" s="7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I6" s="7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J6" s="7">
         <v>0</v>
@@ -1683,7 +1683,7 @@
         <v>39</v>
       </c>
       <c r="L6" s="7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M6" s="7">
         <v>26</v>
@@ -1701,7 +1701,7 @@
         <v>0</v>
       </c>
       <c r="R6" s="7">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S6" s="7">
         <v>26</v>
@@ -1728,16 +1728,16 @@
         <v>27</v>
       </c>
       <c r="AA6" s="7">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB6" s="7">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AC6" s="7">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AD6" s="7">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AE6" s="7">
         <v>0</v>
@@ -1757,19 +1757,19 @@
         <v>0</v>
       </c>
       <c r="D7" s="7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G7" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H7" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" s="7">
         <v>23</v>
@@ -1778,19 +1778,19 @@
         <v>0</v>
       </c>
       <c r="K7" s="7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L7" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M7" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N7" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O7" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P7" s="7">
         <v>23</v>
@@ -1808,31 +1808,31 @@
         <v>18</v>
       </c>
       <c r="U7" s="7">
+        <v>17</v>
+      </c>
+      <c r="V7" s="7">
+        <v>17</v>
+      </c>
+      <c r="W7" s="7">
+        <v>23</v>
+      </c>
+      <c r="X7" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="7">
+        <v>27</v>
+      </c>
+      <c r="Z7" s="7">
         <v>18</v>
       </c>
-      <c r="V7" s="7">
+      <c r="AA7" s="7">
         <v>18</v>
       </c>
-      <c r="W7" s="7">
-        <v>24</v>
-      </c>
-      <c r="X7" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="7">
-        <v>28</v>
-      </c>
-      <c r="Z7" s="7">
-        <v>19</v>
-      </c>
-      <c r="AA7" s="7">
-        <v>19</v>
-      </c>
       <c r="AB7" s="7">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AC7" s="7">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AD7" s="7">
         <v>24</v>
@@ -1841,7 +1841,7 @@
         <v>0</v>
       </c>
       <c r="AF7" s="7">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.45">
@@ -1870,7 +1870,7 @@
         <v>15</v>
       </c>
       <c r="I8" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J8" s="7">
         <v>0</v>
@@ -1888,10 +1888,10 @@
         <v>15</v>
       </c>
       <c r="O8" s="7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P8" s="7">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q8" s="7">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>24</v>
       </c>
       <c r="S8" s="7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T8" s="7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U8" s="7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V8" s="7">
         <v>16</v>
       </c>
       <c r="W8" s="7">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="X8" s="7">
         <v>0</v>
@@ -1930,7 +1930,7 @@
         <v>16</v>
       </c>
       <c r="AC8" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AD8" s="7">
         <v>21</v>
@@ -1947,7 +1947,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" s="7">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>17</v>
       </c>
       <c r="I9" s="7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J9" s="7">
         <v>0</v>
@@ -1989,19 +1989,19 @@
         <v>17</v>
       </c>
       <c r="P9" s="7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q9" s="7">
         <v>0</v>
       </c>
       <c r="R9" s="7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S9" s="7">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T9" s="7">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U9" s="7">
         <v>18</v>
@@ -2016,10 +2016,10 @@
         <v>0</v>
       </c>
       <c r="Y9" s="7">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z9" s="7">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA9" s="7">
         <v>19</v>
@@ -2028,16 +2028,16 @@
         <v>19</v>
       </c>
       <c r="AC9" s="7">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AD9" s="7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE9" s="7">
         <v>0</v>
       </c>
       <c r="AF9" s="7">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.45">
@@ -2045,13 +2045,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" s="7">
         <v>0</v>
       </c>
       <c r="D10" s="7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E10" s="7">
         <v>16</v>
@@ -2072,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L10" s="7">
         <v>16</v>
@@ -2096,16 +2096,16 @@
         <v>25</v>
       </c>
       <c r="S10" s="7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T10" s="7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U10" s="7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V10" s="7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W10" s="7">
         <v>22</v>
@@ -2114,7 +2114,7 @@
         <v>0</v>
       </c>
       <c r="Y10" s="7">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z10" s="7">
         <v>17</v>
@@ -2135,7 +2135,7 @@
         <v>0</v>
       </c>
       <c r="AF10" s="7">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -2281,7 +2281,7 @@
         <v>6</v>
       </c>
       <c r="I2" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J2" s="4">
         <v>0</v>
@@ -2302,7 +2302,7 @@
         <v>6</v>
       </c>
       <c r="P2" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q2" s="4">
         <v>0</v>
@@ -2317,7 +2317,7 @@
         <v>6</v>
       </c>
       <c r="U2" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V2" s="4">
         <v>6</v>
@@ -2338,10 +2338,10 @@
         <v>6</v>
       </c>
       <c r="AB2" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC2" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD2" s="4">
         <v>9</v>
@@ -2350,7 +2350,7 @@
         <v>0</v>
       </c>
       <c r="AF2" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.45">
@@ -2379,7 +2379,7 @@
         <v>5</v>
       </c>
       <c r="I3" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J3" s="4">
         <v>0</v>
@@ -2415,10 +2415,10 @@
         <v>5</v>
       </c>
       <c r="U3" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V3" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W3" s="4">
         <v>7</v>
@@ -2436,10 +2436,10 @@
         <v>6</v>
       </c>
       <c r="AB3" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC3" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD3" s="4">
         <v>8</v>
@@ -2448,7 +2448,7 @@
         <v>0</v>
       </c>
       <c r="AF3" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.45">
@@ -2513,13 +2513,13 @@
         <v>6</v>
       </c>
       <c r="U4" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V4" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W4" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X4" s="4">
         <v>0</v>
@@ -2537,7 +2537,7 @@
         <v>6</v>
       </c>
       <c r="AC4" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD4" s="4">
         <v>7</v>
@@ -2546,7 +2546,7 @@
         <v>0</v>
       </c>
       <c r="AF4" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.45">
@@ -2554,7 +2554,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="4">
         <v>0</v>
@@ -2575,7 +2575,7 @@
         <v>6</v>
       </c>
       <c r="I5" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J5" s="4">
         <v>0</v>
@@ -2596,7 +2596,7 @@
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q5" s="4">
         <v>0</v>
@@ -2635,7 +2635,7 @@
         <v>6</v>
       </c>
       <c r="AC5" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD5" s="4">
         <v>7</v>
@@ -2644,7 +2644,7 @@
         <v>0</v>
       </c>
       <c r="AF5" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.45">
@@ -2661,16 +2661,16 @@
         <v>11</v>
       </c>
       <c r="E6" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I6" s="4">
         <v>10</v>
@@ -2682,7 +2682,7 @@
         <v>11</v>
       </c>
       <c r="L6" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M6" s="4">
         <v>7</v>
@@ -2730,19 +2730,19 @@
         <v>8</v>
       </c>
       <c r="AB6" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC6" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD6" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE6" s="4">
         <v>0</v>
       </c>
       <c r="AF6" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.45">
@@ -2807,13 +2807,13 @@
         <v>6</v>
       </c>
       <c r="U7" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V7" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W7" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X7" s="4">
         <v>0</v>
@@ -2831,7 +2831,7 @@
         <v>6</v>
       </c>
       <c r="AC7" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD7" s="4">
         <v>7</v>
@@ -2840,7 +2840,7 @@
         <v>0</v>
       </c>
       <c r="AF7" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.45">
@@ -2908,7 +2908,7 @@
         <v>5</v>
       </c>
       <c r="V8" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W8" s="4">
         <v>7</v>
@@ -2932,13 +2932,13 @@
         <v>5</v>
       </c>
       <c r="AD8" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE8" s="4">
         <v>0</v>
       </c>
       <c r="AF8" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.45">
@@ -2946,13 +2946,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" s="4">
         <v>0</v>
       </c>
       <c r="D9" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E9" s="4">
         <v>4</v>
@@ -2973,7 +2973,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L9" s="4">
         <v>4</v>
@@ -2988,13 +2988,13 @@
         <v>4</v>
       </c>
       <c r="P9" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q9" s="4">
         <v>0</v>
       </c>
       <c r="R9" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S9" s="4">
         <v>4</v>
@@ -3003,10 +3003,10 @@
         <v>4</v>
       </c>
       <c r="U9" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V9" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W9" s="4">
         <v>6</v>
@@ -3036,7 +3036,7 @@
         <v>0</v>
       </c>
       <c r="AF9" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.45">
@@ -3077,13 +3077,13 @@
         <v>5</v>
       </c>
       <c r="M10" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N10" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O10" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P10" s="4">
         <v>7</v>
@@ -3095,10 +3095,10 @@
         <v>8</v>
       </c>
       <c r="S10" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T10" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U10" s="4">
         <v>5</v>
@@ -3116,25 +3116,25 @@
         <v>8</v>
       </c>
       <c r="Z10" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA10" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB10" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC10" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD10" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE10" s="4">
         <v>0</v>
       </c>
       <c r="AF10" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/target.xlsx
+++ b/target.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\백업폴더\딱따구리\AI\강북도매 영업관리 포털\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7851EAEA-3845-462A-8B2E-E8F57C382B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38651BEB-E238-4782-BA3D-DDB01270892A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F51F585E-D8DA-4EE1-A615-D4BBA305B88C}"/>
   </bookViews>
@@ -1254,61 +1254,61 @@
         <v>1</v>
       </c>
       <c r="B2" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2" s="6">
         <v>0</v>
       </c>
       <c r="H2" s="6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I2" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J2" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L2" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M2" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N2" s="6">
         <v>0</v>
       </c>
       <c r="O2" s="6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P2" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R2" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S2" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T2" s="6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="U2" s="6">
         <v>0</v>
@@ -1317,31 +1317,31 @@
         <v>30</v>
       </c>
       <c r="W2" s="6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="X2" s="6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Y2" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z2" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA2" s="6">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AB2" s="6">
         <v>0</v>
       </c>
       <c r="AC2" s="6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AD2" s="6">
         <v>20</v>
       </c>
       <c r="AE2" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.45">
@@ -1349,88 +1349,88 @@
         <v>0</v>
       </c>
       <c r="B3" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3" s="6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3" s="6">
         <v>0</v>
       </c>
       <c r="H3" s="6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I3" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J3" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K3" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L3" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M3" s="6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N3" s="6">
         <v>0</v>
       </c>
       <c r="O3" s="6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P3" s="6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q3" s="6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="R3" s="6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="S3" s="6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="T3" s="6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U3" s="6">
         <v>0</v>
       </c>
       <c r="V3" s="6">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="W3" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X3" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y3" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z3" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA3" s="6">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AB3" s="6">
         <v>0</v>
       </c>
       <c r="AC3" s="6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AD3" s="6">
         <v>18</v>
@@ -1444,31 +1444,31 @@
         <v>2</v>
       </c>
       <c r="B4" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4" s="6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G4" s="6">
         <v>0</v>
       </c>
       <c r="H4" s="6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I4" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J4" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K4" s="6">
         <v>14</v>
@@ -1477,13 +1477,13 @@
         <v>14</v>
       </c>
       <c r="M4" s="6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N4" s="6">
         <v>0</v>
       </c>
       <c r="O4" s="6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P4" s="6">
         <v>14</v>
@@ -1498,13 +1498,13 @@
         <v>14</v>
       </c>
       <c r="T4" s="6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U4" s="6">
         <v>0</v>
       </c>
       <c r="V4" s="6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="W4" s="6">
         <v>14</v>
@@ -1513,13 +1513,13 @@
         <v>14</v>
       </c>
       <c r="Y4" s="6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z4" s="6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA4" s="6">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AB4" s="6">
         <v>0</v>
@@ -1539,73 +1539,73 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5" s="6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G5" s="6">
         <v>0</v>
       </c>
       <c r="H5" s="6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I5" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J5" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K5" s="6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L5" s="6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M5" s="6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N5" s="6">
         <v>0</v>
       </c>
       <c r="O5" s="6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P5" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q5" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R5" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S5" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T5" s="6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U5" s="6">
         <v>0</v>
       </c>
       <c r="V5" s="6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="W5" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X5" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y5" s="6">
         <v>20</v>
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="AA5" s="6">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="6">
         <v>0</v>
@@ -1634,82 +1634,82 @@
         <v>3</v>
       </c>
       <c r="B6" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6" s="6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G6" s="6">
         <v>0</v>
       </c>
       <c r="H6" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I6" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J6" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K6" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L6" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M6" s="6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N6" s="6">
         <v>0</v>
       </c>
       <c r="O6" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P6" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q6" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R6" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S6" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T6" s="6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U6" s="6">
         <v>0</v>
       </c>
       <c r="V6" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W6" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X6" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y6" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z6" s="6">
         <v>17</v>
       </c>
       <c r="AA6" s="6">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="6">
         <v>0</v>
@@ -1729,91 +1729,91 @@
         <v>8</v>
       </c>
       <c r="B7" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F7" s="6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G7" s="6">
         <v>0</v>
       </c>
       <c r="H7" s="6">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I7" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J7" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K7" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L7" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M7" s="6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N7" s="6">
         <v>0</v>
       </c>
       <c r="O7" s="6">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="P7" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q7" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R7" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S7" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T7" s="6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="U7" s="6">
         <v>0</v>
       </c>
       <c r="V7" s="6">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="W7" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="X7" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y7" s="6">
         <v>24</v>
       </c>
       <c r="Z7" s="6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA7" s="6">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="6">
         <v>0</v>
       </c>
       <c r="AC7" s="6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AD7" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE7" s="6">
         <v>24</v>
@@ -1824,73 +1824,73 @@
         <v>5</v>
       </c>
       <c r="B8" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D8" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E8" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F8" s="6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G8" s="6">
         <v>0</v>
       </c>
       <c r="H8" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I8" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J8" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K8" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L8" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M8" s="6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N8" s="6">
         <v>0</v>
       </c>
       <c r="O8" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P8" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q8" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R8" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S8" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T8" s="6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U8" s="6">
         <v>0</v>
       </c>
       <c r="V8" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="W8" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X8" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y8" s="6">
         <v>16</v>
@@ -1899,13 +1899,13 @@
         <v>16</v>
       </c>
       <c r="AA8" s="6">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="6">
         <v>0</v>
       </c>
       <c r="AC8" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AD8" s="6">
         <v>16</v>
@@ -1919,16 +1919,16 @@
         <v>6</v>
       </c>
       <c r="B9" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E9" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F9" s="6">
         <v>19</v>
@@ -1937,19 +1937,19 @@
         <v>0</v>
       </c>
       <c r="H9" s="6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I9" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J9" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K9" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L9" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M9" s="6">
         <v>19</v>
@@ -1958,19 +1958,19 @@
         <v>0</v>
       </c>
       <c r="O9" s="6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q9" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R9" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S9" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T9" s="6">
         <v>19</v>
@@ -1979,22 +1979,22 @@
         <v>0</v>
       </c>
       <c r="V9" s="6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W9" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X9" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y9" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z9" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA9" s="6">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="6">
         <v>0</v>
@@ -2003,7 +2003,7 @@
         <v>22</v>
       </c>
       <c r="AD9" s="6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE9" s="6">
         <v>14</v>
@@ -2014,16 +2014,16 @@
         <v>7</v>
       </c>
       <c r="B10" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E10" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F10" s="6">
         <v>20</v>
@@ -2032,19 +2032,19 @@
         <v>0</v>
       </c>
       <c r="H10" s="6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I10" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J10" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K10" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L10" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M10" s="6">
         <v>20</v>
@@ -2053,19 +2053,19 @@
         <v>0</v>
       </c>
       <c r="O10" s="6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P10" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q10" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R10" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S10" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T10" s="6">
         <v>20</v>
@@ -2074,13 +2074,13 @@
         <v>0</v>
       </c>
       <c r="V10" s="6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W10" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X10" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y10" s="6">
         <v>15</v>
@@ -2089,7 +2089,7 @@
         <v>15</v>
       </c>
       <c r="AA10" s="6">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AB10" s="6">
         <v>0</v>
@@ -2101,7 +2101,7 @@
         <v>15</v>
       </c>
       <c r="AE10" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -2223,16 +2223,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" s="3">
         <v>7</v>
@@ -2241,19 +2241,19 @@
         <v>0</v>
       </c>
       <c r="H2" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M2" s="3">
         <v>7</v>
@@ -2265,16 +2265,16 @@
         <v>8</v>
       </c>
       <c r="P2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R2" s="3">
         <v>6</v>
       </c>
       <c r="S2" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T2" s="3">
         <v>7</v>
@@ -2298,7 +2298,7 @@
         <v>5</v>
       </c>
       <c r="AA2" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AB2" s="3">
         <v>0</v>
@@ -2330,76 +2330,76 @@
         <v>6</v>
       </c>
       <c r="F3" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
       </c>
       <c r="H3" s="3">
+        <v>9</v>
+      </c>
+      <c r="I3" s="3">
+        <v>6</v>
+      </c>
+      <c r="J3" s="3">
+        <v>6</v>
+      </c>
+      <c r="K3" s="3">
+        <v>6</v>
+      </c>
+      <c r="L3" s="3">
+        <v>6</v>
+      </c>
+      <c r="M3" s="3">
         <v>8</v>
       </c>
-      <c r="I3" s="3">
-        <v>6</v>
-      </c>
-      <c r="J3" s="3">
-        <v>6</v>
-      </c>
-      <c r="K3" s="3">
-        <v>6</v>
-      </c>
-      <c r="L3" s="3">
-        <v>6</v>
-      </c>
-      <c r="M3" s="3">
-        <v>7</v>
-      </c>
       <c r="N3" s="3">
         <v>0</v>
       </c>
       <c r="O3" s="3">
+        <v>9</v>
+      </c>
+      <c r="P3" s="3">
+        <v>6</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>6</v>
+      </c>
+      <c r="R3" s="3">
+        <v>6</v>
+      </c>
+      <c r="S3" s="3">
+        <v>6</v>
+      </c>
+      <c r="T3" s="3">
         <v>8</v>
       </c>
-      <c r="P3" s="3">
-        <v>5</v>
-      </c>
-      <c r="Q3" s="3">
-        <v>5</v>
-      </c>
-      <c r="R3" s="3">
-        <v>5</v>
-      </c>
-      <c r="S3" s="3">
-        <v>5</v>
-      </c>
-      <c r="T3" s="3">
-        <v>7</v>
-      </c>
       <c r="U3" s="3">
         <v>0</v>
       </c>
       <c r="V3" s="3">
+        <v>9</v>
+      </c>
+      <c r="W3" s="3">
+        <v>6</v>
+      </c>
+      <c r="X3" s="3">
+        <v>6</v>
+      </c>
+      <c r="Y3" s="3">
+        <v>6</v>
+      </c>
+      <c r="Z3" s="3">
+        <v>6</v>
+      </c>
+      <c r="AA3" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="3">
         <v>8</v>
-      </c>
-      <c r="W3" s="3">
-        <v>6</v>
-      </c>
-      <c r="X3" s="3">
-        <v>6</v>
-      </c>
-      <c r="Y3" s="3">
-        <v>6</v>
-      </c>
-      <c r="Z3" s="3">
-        <v>6</v>
-      </c>
-      <c r="AA3" s="3">
-        <v>8</v>
-      </c>
-      <c r="AB3" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="3">
-        <v>9</v>
       </c>
       <c r="AD3" s="3">
         <v>6</v>
@@ -2425,13 +2425,13 @@
         <v>5</v>
       </c>
       <c r="F4" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
       </c>
       <c r="H4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I4" s="3">
         <v>5</v>
@@ -2446,13 +2446,13 @@
         <v>5</v>
       </c>
       <c r="M4" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N4" s="3">
         <v>0</v>
       </c>
       <c r="O4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P4" s="3">
         <v>5</v>
@@ -2467,13 +2467,13 @@
         <v>5</v>
       </c>
       <c r="T4" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U4" s="3">
         <v>0</v>
       </c>
       <c r="V4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W4" s="3">
         <v>5</v>
@@ -2488,7 +2488,7 @@
         <v>5</v>
       </c>
       <c r="AA4" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AB4" s="3">
         <v>0</v>
@@ -2526,7 +2526,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="3">
         <v>5</v>
@@ -2547,16 +2547,16 @@
         <v>0</v>
       </c>
       <c r="O5" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P5" s="3">
         <v>5</v>
       </c>
       <c r="Q5" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R5" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S5" s="3">
         <v>6</v>
@@ -2571,25 +2571,25 @@
         <v>8</v>
       </c>
       <c r="W5" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X5" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y5" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z5" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA5" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="3">
         <v>0</v>
       </c>
       <c r="AC5" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD5" s="3">
         <v>6</v>
@@ -2603,16 +2603,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" s="3">
         <v>7</v>
@@ -2624,16 +2624,16 @@
         <v>8</v>
       </c>
       <c r="I6" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J6" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K6" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L6" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M6" s="3">
         <v>7</v>
@@ -2642,29 +2642,29 @@
         <v>0</v>
       </c>
       <c r="O6" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P6" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q6" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R6" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S6" s="3">
         <v>5</v>
       </c>
       <c r="T6" s="3">
+        <v>7</v>
+      </c>
+      <c r="U6" s="3">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3">
         <v>8</v>
       </c>
-      <c r="U6" s="3">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3">
-        <v>9</v>
-      </c>
       <c r="W6" s="3">
         <v>5</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>5</v>
       </c>
       <c r="AA6" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="3">
         <v>0</v>
@@ -2710,55 +2710,55 @@
         <v>7</v>
       </c>
       <c r="F7" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
       </c>
       <c r="H7" s="3">
+        <v>11</v>
+      </c>
+      <c r="I7" s="3">
+        <v>7</v>
+      </c>
+      <c r="J7" s="3">
+        <v>7</v>
+      </c>
+      <c r="K7" s="3">
+        <v>7</v>
+      </c>
+      <c r="L7" s="3">
+        <v>7</v>
+      </c>
+      <c r="M7" s="3">
         <v>10</v>
       </c>
-      <c r="I7" s="3">
-        <v>7</v>
-      </c>
-      <c r="J7" s="3">
-        <v>7</v>
-      </c>
-      <c r="K7" s="3">
-        <v>7</v>
-      </c>
-      <c r="L7" s="3">
-        <v>7</v>
-      </c>
-      <c r="M7" s="3">
-        <v>9</v>
-      </c>
       <c r="N7" s="3">
         <v>0</v>
       </c>
       <c r="O7" s="3">
+        <v>11</v>
+      </c>
+      <c r="P7" s="3">
+        <v>7</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>7</v>
+      </c>
+      <c r="R7" s="3">
+        <v>7</v>
+      </c>
+      <c r="S7" s="3">
+        <v>7</v>
+      </c>
+      <c r="T7" s="3">
         <v>10</v>
       </c>
-      <c r="P7" s="3">
-        <v>7</v>
-      </c>
-      <c r="Q7" s="3">
-        <v>6</v>
-      </c>
-      <c r="R7" s="3">
-        <v>6</v>
-      </c>
-      <c r="S7" s="3">
-        <v>6</v>
-      </c>
-      <c r="T7" s="3">
-        <v>9</v>
-      </c>
       <c r="U7" s="3">
         <v>0</v>
       </c>
       <c r="V7" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W7" s="3">
         <v>7</v>
@@ -2773,13 +2773,13 @@
         <v>7</v>
       </c>
       <c r="AA7" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="3">
         <v>0</v>
       </c>
       <c r="AC7" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AD7" s="3">
         <v>7</v>
@@ -2841,10 +2841,10 @@
         <v>4</v>
       </c>
       <c r="R8" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S8" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T8" s="3">
         <v>5</v>
@@ -2856,10 +2856,10 @@
         <v>6</v>
       </c>
       <c r="W8" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X8" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y8" s="3">
         <v>4</v>
@@ -2868,7 +2868,7 @@
         <v>4</v>
       </c>
       <c r="AA8" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="3">
         <v>0</v>
@@ -2888,19 +2888,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
@@ -2909,19 +2909,19 @@
         <v>7</v>
       </c>
       <c r="I9" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J9" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K9" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L9" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M9" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N9" s="3">
         <v>0</v>
@@ -2963,7 +2963,7 @@
         <v>5</v>
       </c>
       <c r="AA9" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="3">
         <v>0</v>
@@ -2995,13 +2995,13 @@
         <v>5</v>
       </c>
       <c r="F10" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G10" s="3">
         <v>0</v>
       </c>
       <c r="H10" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I10" s="3">
         <v>5</v>
@@ -3016,13 +3016,13 @@
         <v>5</v>
       </c>
       <c r="M10" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N10" s="3">
         <v>0</v>
       </c>
       <c r="O10" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P10" s="3">
         <v>5</v>
@@ -3037,13 +3037,13 @@
         <v>5</v>
       </c>
       <c r="T10" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U10" s="3">
         <v>0</v>
       </c>
       <c r="V10" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W10" s="3">
         <v>5</v>
@@ -3058,7 +3058,7 @@
         <v>5</v>
       </c>
       <c r="AA10" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AB10" s="3">
         <v>0</v>
